--- a/AnalisisFinanciero/data/890903939_2024-12-31_Notas_Arrendamientos_traduccion.xlsx
+++ b/AnalisisFinanciero/data/890903939_2024-12-31_Notas_Arrendamientos_traduccion.xlsx
@@ -1,12 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E98714C-4373-4429-B3A0-3D58713A66E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Hoja1" state="visible" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -112,35 +137,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
+      <family val="2"/>
     </font>
     <font>
-      <color theme="1"/>
-      <sz val="9"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font/>
-    <font>
-      <sz val="9"/>
-      <name val="Helvetica Neue"/>
+      <name val="Arial"/>
+      <sz val="10.00"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,24 +177,96 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -179,52 +279,10 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -257,8 +315,12 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -277,73 +339,319 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="3" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" applyBorder="1"/>
+    <xf fontId="4" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="9" applyFill="1" borderId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" applyBorder="1"/>
+    <xf borderId="13" applyBorder="1"/>
+    <xf fontId="4" applyFont="1" fillId="12" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" applyFont="1" fillId="13" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="14" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="4" applyFont="1" fillId="15" applyFill="1" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf borderId="19" applyBorder="1"/>
+    <xf fontId="4" applyFont="1" fillId="16" applyFill="1" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" borderId="21" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
+    <xf xfId="4" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="19" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="15" applyFill="1" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="13" quotePrefix="0" pivotButton="0" borderId="12" applyBorder="1"/>
+    <xf xfId="20" quotePrefix="0" pivotButton="0" borderId="19" applyBorder="1"/>
+    <xf xfId="7" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="16" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="13" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="15" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="12" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="12" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="14" quotePrefix="0" pivotButton="0" borderId="13" applyBorder="1"/>
+    <xf xfId="10" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="9" applyFill="1" borderId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="8" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="6" quotePrefix="0" pivotButton="0" borderId="5" applyBorder="1"/>
+    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="21" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="16" applyFill="1" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="22" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="21" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="18" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="14" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="9" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="2" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="11" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="17" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -359,56 +667,116 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -446,15 +814,15 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
@@ -515,32 +883,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
+            <a:satMod val="170000"/>
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:satMod val="120000"/>
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -549,21 +917,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W1000"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.00" customHeight="1" defaultColWidth="14.47"/>
   <cols>
-    <col min="1" max="1" width="3.43" customWidth="1"/>
-    <col min="2" max="2" width="63" customWidth="1"/>
-    <col min="3" max="23" width="18.86" customWidth="1"/>
-    <col min="24" max="26" width="11.57" customWidth="1"/>
+    <col min="1" max="1" width="3.43" customWidth="1" hidden="0"/>
+    <col min="2" max="2" width="63.04" customWidth="1" hidden="0"/>
+    <col min="3" max="23" width="18.89" customWidth="1" hidden="0"/>
+    <col min="24" max="26" width="11.53" customWidth="1" hidden="0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" ht="12.75" customHeight="true">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
@@ -590,7 +966,7 @@
       <c r="V1" s="3"/>
       <c r="W1" s="4"/>
     </row>
-    <row r="2" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" ht="12.75" customHeight="true">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="5" t="s">
@@ -621,7 +997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" ht="12.75" customHeight="true">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -672,7 +1048,7 @@
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
     </row>
-    <row r="4" ht="27.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" ht="27.75" customHeight="true">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="10" t="s">
@@ -707,7 +1083,7 @@
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
     </row>
-    <row r="5" ht="27.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" ht="27.75" customHeight="true">
       <c r="A5" s="15" t="s">
         <v>22</v>
       </c>
@@ -734,7 +1110,7 @@
       <c r="V5" s="16"/>
       <c r="W5" s="16"/>
     </row>
-    <row r="6" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" ht="12.75" customHeight="true">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
         <v>23</v>
@@ -773,7 +1149,7 @@
       <c r="V6" s="19"/>
       <c r="W6" s="19"/>
     </row>
-    <row r="7" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" ht="12.75" customHeight="true">
       <c r="A7" s="17"/>
       <c r="B7" s="20" t="s">
         <v>24</v>
@@ -800,7 +1176,7 @@
       <c r="V7" s="19"/>
       <c r="W7" s="19"/>
     </row>
-    <row r="8" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" ht="12.75" customHeight="true">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
         <v>25</v>
@@ -839,7 +1215,7 @@
       <c r="V8" s="16"/>
       <c r="W8" s="16"/>
     </row>
-    <row r="9" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" ht="12.75" customHeight="true">
       <c r="A9" s="17"/>
       <c r="B9" s="20" t="s">
         <v>26</v>
@@ -866,7 +1242,7 @@
       <c r="V9" s="19"/>
       <c r="W9" s="19"/>
     </row>
-    <row r="10" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" ht="12.75" customHeight="true">
       <c r="A10" s="17"/>
       <c r="B10" s="18" t="s">
         <v>27</v>
@@ -893,7 +1269,7 @@
       <c r="V10" s="16"/>
       <c r="W10" s="16"/>
     </row>
-    <row r="11" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" ht="12.75" customHeight="true">
       <c r="A11" s="17"/>
       <c r="B11" s="20" t="s">
         <v>28</v>
@@ -934,7 +1310,7 @@
       <c r="V11" s="19"/>
       <c r="W11" s="19"/>
     </row>
-    <row r="12" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" ht="12.75" customHeight="true">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
         <v>29</v>
@@ -961,7 +1337,7 @@
       <c r="V12" s="16"/>
       <c r="W12" s="16"/>
     </row>
-    <row r="13" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" ht="12.75" customHeight="true">
       <c r="A13" s="17"/>
       <c r="B13" s="20" t="s">
         <v>30</v>
@@ -988,7 +1364,7 @@
       <c r="V13" s="19"/>
       <c r="W13" s="19"/>
     </row>
-    <row r="14" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" ht="12.75" customHeight="true">
       <c r="A14" s="21"/>
       <c r="B14" s="18" t="s">
         <v>31</v>
@@ -1015,7 +1391,7 @@
       <c r="V14" s="22"/>
       <c r="W14" s="22"/>
     </row>
-    <row r="15" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" ht="12.75" customHeight="true">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1040,7 +1416,7 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
     </row>
-    <row r="16" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" ht="12.75" customHeight="true">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1065,7 +1441,7 @@
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
     </row>
-    <row r="17" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" ht="12.75" customHeight="true">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1090,7 +1466,7 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
     </row>
-    <row r="18" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" ht="12.75" customHeight="true">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1115,7 +1491,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" ht="12.75" customHeight="true">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1140,7 +1516,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" ht="12.75" customHeight="true">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1165,7 +1541,7 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" ht="12.75" customHeight="true">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1190,7 +1566,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" ht="12.75" customHeight="true">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1215,7 +1591,7 @@
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
     </row>
-    <row r="23" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" ht="12.75" customHeight="true">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1240,7 +1616,7 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
     </row>
-    <row r="24" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" ht="12.75" customHeight="true">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1265,7 +1641,7 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
     </row>
-    <row r="25" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" ht="12.75" customHeight="true">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1290,7 +1666,7 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
     </row>
-    <row r="26" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" ht="12.75" customHeight="true">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1315,7 +1691,7 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
     </row>
-    <row r="27" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" ht="12.75" customHeight="true">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1340,7 +1716,7 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
-    <row r="28" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" ht="12.75" customHeight="true">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1365,7 +1741,7 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
     </row>
-    <row r="29" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" ht="12.75" customHeight="true">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1390,7 +1766,7 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
     </row>
-    <row r="30" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" ht="12.75" customHeight="true">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1415,7 +1791,7 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
     </row>
-    <row r="31" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" ht="12.75" customHeight="true">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1440,7 +1816,7 @@
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
     </row>
-    <row r="32" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" ht="12.75" customHeight="true">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1465,7 +1841,7 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
     </row>
-    <row r="33" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" ht="12.75" customHeight="true">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1490,7 +1866,7 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
     </row>
-    <row r="34" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" ht="12.75" customHeight="true">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1515,7 +1891,7 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
     </row>
-    <row r="35" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" ht="12.75" customHeight="true">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1540,7 +1916,7 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
-    <row r="36" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" ht="12.75" customHeight="true">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1565,7 +1941,7 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
-    <row r="37" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" ht="12.75" customHeight="true">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1590,7 +1966,7 @@
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
     </row>
-    <row r="38" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" ht="12.75" customHeight="true">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1615,7 +1991,7 @@
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
     </row>
-    <row r="39" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" ht="12.75" customHeight="true">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1640,7 +2016,7 @@
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" ht="12.75" customHeight="true">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1665,7 +2041,7 @@
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
     </row>
-    <row r="41" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" ht="12.75" customHeight="true">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1690,7 +2066,7 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" ht="12.75" customHeight="true">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1715,7 +2091,7 @@
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" ht="12.75" customHeight="true">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1740,7 +2116,7 @@
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
     </row>
-    <row r="44" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" ht="12.75" customHeight="true">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1765,7 +2141,7 @@
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
     </row>
-    <row r="45" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" ht="12.75" customHeight="true">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1790,7 +2166,7 @@
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
     </row>
-    <row r="46" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" ht="12.75" customHeight="true">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1815,7 +2191,7 @@
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
     </row>
-    <row r="47" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" ht="12.75" customHeight="true">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1840,7 +2216,7 @@
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
     </row>
-    <row r="48" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" ht="12.75" customHeight="true">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1865,7 +2241,7 @@
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
     </row>
-    <row r="49" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" ht="12.75" customHeight="true">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1890,7 +2266,7 @@
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
     </row>
-    <row r="50" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" ht="12.75" customHeight="true">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1915,7 +2291,7 @@
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
     </row>
-    <row r="51" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" ht="12.75" customHeight="true">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1940,7 +2316,7 @@
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
     </row>
-    <row r="52" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" ht="12.75" customHeight="true">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1965,7 +2341,7 @@
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
     </row>
-    <row r="53" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" ht="12.75" customHeight="true">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1990,7 +2366,7 @@
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
     </row>
-    <row r="54" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" ht="12.75" customHeight="true">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2015,7 +2391,7 @@
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
     </row>
-    <row r="55" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" ht="12.75" customHeight="true">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2040,7 +2416,7 @@
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
     </row>
-    <row r="56" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" ht="12.75" customHeight="true">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2065,7 +2441,7 @@
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
     </row>
-    <row r="57" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" ht="12.75" customHeight="true">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2090,7 +2466,7 @@
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
     </row>
-    <row r="58" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" ht="12.75" customHeight="true">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2115,7 +2491,7 @@
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
     </row>
-    <row r="59" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" ht="12.75" customHeight="true">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2140,7 +2516,7 @@
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
     </row>
-    <row r="60" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" ht="12.75" customHeight="true">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2165,7 +2541,7 @@
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
     </row>
-    <row r="61" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" ht="12.75" customHeight="true">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2190,7 +2566,7 @@
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
     </row>
-    <row r="62" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" ht="12.75" customHeight="true">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2215,7 +2591,7 @@
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
     </row>
-    <row r="63" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" ht="12.75" customHeight="true">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2240,7 +2616,7 @@
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
     </row>
-    <row r="64" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" ht="12.75" customHeight="true">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2265,7 +2641,7 @@
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
     </row>
-    <row r="65" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" ht="12.75" customHeight="true">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2290,7 +2666,7 @@
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
     </row>
-    <row r="66" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" ht="12.75" customHeight="true">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2315,7 +2691,7 @@
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
     </row>
-    <row r="67" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" ht="12.75" customHeight="true">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2340,7 +2716,7 @@
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
     </row>
-    <row r="68" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" ht="12.75" customHeight="true">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2365,7 +2741,7 @@
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
     </row>
-    <row r="69" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" ht="12.75" customHeight="true">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2390,7 +2766,7 @@
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
     </row>
-    <row r="70" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" ht="12.75" customHeight="true">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2415,7 +2791,7 @@
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
     </row>
-    <row r="71" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" ht="12.75" customHeight="true">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2440,7 +2816,7 @@
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
     </row>
-    <row r="72" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="72" ht="12.75" customHeight="true">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2465,7 +2841,7 @@
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
     </row>
-    <row r="73" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" ht="12.75" customHeight="true">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2490,7 +2866,7 @@
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
     </row>
-    <row r="74" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" ht="12.75" customHeight="true">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2515,7 +2891,7 @@
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
     </row>
-    <row r="75" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" ht="12.75" customHeight="true">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2540,7 +2916,7 @@
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
     </row>
-    <row r="76" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" ht="12.75" customHeight="true">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2565,7 +2941,7 @@
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
     </row>
-    <row r="77" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" ht="12.75" customHeight="true">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2590,7 +2966,7 @@
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
     </row>
-    <row r="78" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" ht="12.75" customHeight="true">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2615,7 +2991,7 @@
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
     </row>
-    <row r="79" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" ht="12.75" customHeight="true">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2640,7 +3016,7 @@
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
     </row>
-    <row r="80" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" ht="12.75" customHeight="true">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2665,7 +3041,7 @@
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
     </row>
-    <row r="81" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" ht="12.75" customHeight="true">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2690,7 +3066,7 @@
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
     </row>
-    <row r="82" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" ht="12.75" customHeight="true">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2715,7 +3091,7 @@
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
     </row>
-    <row r="83" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" ht="12.75" customHeight="true">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2740,7 +3116,7 @@
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
     </row>
-    <row r="84" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" ht="12.75" customHeight="true">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2765,7 +3141,7 @@
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
     </row>
-    <row r="85" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" ht="12.75" customHeight="true">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2790,7 +3166,7 @@
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
     </row>
-    <row r="86" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" ht="12.75" customHeight="true">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2815,7 +3191,7 @@
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
     </row>
-    <row r="87" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" ht="12.75" customHeight="true">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2840,7 +3216,7 @@
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
     </row>
-    <row r="88" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" ht="12.75" customHeight="true">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2865,7 +3241,7 @@
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
     </row>
-    <row r="89" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" ht="12.75" customHeight="true">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2890,7 +3266,7 @@
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
     </row>
-    <row r="90" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="90" ht="12.75" customHeight="true">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2915,7 +3291,7 @@
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
     </row>
-    <row r="91" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" ht="12.75" customHeight="true">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2940,7 +3316,7 @@
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
     </row>
-    <row r="92" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" ht="12.75" customHeight="true">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2965,7 +3341,7 @@
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
     </row>
-    <row r="93" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" ht="12.75" customHeight="true">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2990,7 +3366,7 @@
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
     </row>
-    <row r="94" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="94" ht="12.75" customHeight="true">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3015,7 +3391,7 @@
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
     </row>
-    <row r="95" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="95" ht="12.75" customHeight="true">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3040,7 +3416,7 @@
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
     </row>
-    <row r="96" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" ht="12.75" customHeight="true">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3065,7 +3441,7 @@
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
     </row>
-    <row r="97" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" ht="12.75" customHeight="true">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3090,7 +3466,7 @@
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
     </row>
-    <row r="98" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="98" ht="12.75" customHeight="true">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3115,7 +3491,7 @@
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
     </row>
-    <row r="99" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" ht="12.75" customHeight="true">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3140,7 +3516,7 @@
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
     </row>
-    <row r="100" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" ht="12.75" customHeight="true">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3165,7 +3541,7 @@
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
     </row>
-    <row r="101" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" ht="12.75" customHeight="true">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3190,7 +3566,7 @@
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
     </row>
-    <row r="102" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="102" ht="12.75" customHeight="true">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3215,7 +3591,7 @@
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
     </row>
-    <row r="103" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="103" ht="12.75" customHeight="true">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3240,7 +3616,7 @@
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
     </row>
-    <row r="104" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="104" ht="12.75" customHeight="true">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3265,7 +3641,7 @@
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
     </row>
-    <row r="105" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="105" ht="12.75" customHeight="true">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3290,7 +3666,7 @@
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
     </row>
-    <row r="106" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="106" ht="12.75" customHeight="true">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3315,7 +3691,7 @@
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
     </row>
-    <row r="107" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="107" ht="12.75" customHeight="true">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3340,7 +3716,7 @@
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
     </row>
-    <row r="108" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="108" ht="12.75" customHeight="true">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3365,7 +3741,7 @@
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
     </row>
-    <row r="109" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="109" ht="12.75" customHeight="true">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3390,7 +3766,7 @@
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
     </row>
-    <row r="110" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="110" ht="12.75" customHeight="true">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3415,7 +3791,7 @@
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
     </row>
-    <row r="111" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="111" ht="12.75" customHeight="true">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3440,7 +3816,7 @@
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
     </row>
-    <row r="112" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="112" ht="12.75" customHeight="true">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3465,7 +3841,7 @@
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
     </row>
-    <row r="113" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="113" ht="12.75" customHeight="true">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3490,7 +3866,7 @@
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
     </row>
-    <row r="114" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="114" ht="12.75" customHeight="true">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3515,7 +3891,7 @@
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
     </row>
-    <row r="115" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="115" ht="12.75" customHeight="true">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3540,7 +3916,7 @@
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
     </row>
-    <row r="116" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="116" ht="12.75" customHeight="true">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3565,7 +3941,7 @@
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
     </row>
-    <row r="117" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="117" ht="12.75" customHeight="true">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3590,7 +3966,7 @@
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
     </row>
-    <row r="118" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="118" ht="12.75" customHeight="true">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3615,7 +3991,7 @@
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
     </row>
-    <row r="119" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="119" ht="12.75" customHeight="true">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3640,7 +4016,7 @@
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
     </row>
-    <row r="120" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="120" ht="12.75" customHeight="true">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3665,7 +4041,7 @@
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
     </row>
-    <row r="121" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="121" ht="12.75" customHeight="true">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3690,7 +4066,7 @@
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
     </row>
-    <row r="122" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="122" ht="12.75" customHeight="true">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3715,7 +4091,7 @@
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
     </row>
-    <row r="123" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="123" ht="12.75" customHeight="true">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3740,7 +4116,7 @@
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
     </row>
-    <row r="124" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="124" ht="12.75" customHeight="true">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3765,7 +4141,7 @@
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
     </row>
-    <row r="125" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="125" ht="12.75" customHeight="true">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3790,7 +4166,7 @@
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
     </row>
-    <row r="126" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="126" ht="12.75" customHeight="true">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3815,7 +4191,7 @@
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
     </row>
-    <row r="127" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="127" ht="12.75" customHeight="true">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3840,7 +4216,7 @@
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
     </row>
-    <row r="128" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="128" ht="12.75" customHeight="true">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3865,7 +4241,7 @@
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
     </row>
-    <row r="129" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="129" ht="12.75" customHeight="true">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -3890,7 +4266,7 @@
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
     </row>
-    <row r="130" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="130" ht="12.75" customHeight="true">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -3915,7 +4291,7 @@
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
     </row>
-    <row r="131" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="131" ht="12.75" customHeight="true">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -3940,7 +4316,7 @@
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
     </row>
-    <row r="132" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="132" ht="12.75" customHeight="true">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -3965,7 +4341,7 @@
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
     </row>
-    <row r="133" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="133" ht="12.75" customHeight="true">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -3990,7 +4366,7 @@
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
     </row>
-    <row r="134" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="134" ht="12.75" customHeight="true">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4015,7 +4391,7 @@
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
     </row>
-    <row r="135" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="135" ht="12.75" customHeight="true">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4040,7 +4416,7 @@
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
     </row>
-    <row r="136" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="136" ht="12.75" customHeight="true">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4065,7 +4441,7 @@
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
     </row>
-    <row r="137" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="137" ht="12.75" customHeight="true">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4090,7 +4466,7 @@
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
     </row>
-    <row r="138" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="138" ht="12.75" customHeight="true">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4115,7 +4491,7 @@
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
     </row>
-    <row r="139" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="139" ht="12.75" customHeight="true">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4140,7 +4516,7 @@
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
     </row>
-    <row r="140" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="140" ht="12.75" customHeight="true">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4165,7 +4541,7 @@
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
     </row>
-    <row r="141" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="141" ht="12.75" customHeight="true">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4190,7 +4566,7 @@
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
     </row>
-    <row r="142" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="142" ht="12.75" customHeight="true">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4215,7 +4591,7 @@
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
     </row>
-    <row r="143" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="143" ht="12.75" customHeight="true">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4240,7 +4616,7 @@
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
     </row>
-    <row r="144" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="144" ht="12.75" customHeight="true">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4265,7 +4641,7 @@
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
     </row>
-    <row r="145" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="145" ht="12.75" customHeight="true">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4290,7 +4666,7 @@
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
     </row>
-    <row r="146" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="146" ht="12.75" customHeight="true">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4315,7 +4691,7 @@
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
     </row>
-    <row r="147" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="147" ht="12.75" customHeight="true">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4340,7 +4716,7 @@
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
     </row>
-    <row r="148" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="148" ht="12.75" customHeight="true">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4365,7 +4741,7 @@
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
     </row>
-    <row r="149" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="149" ht="12.75" customHeight="true">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4390,7 +4766,7 @@
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
     </row>
-    <row r="150" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="150" ht="12.75" customHeight="true">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4415,7 +4791,7 @@
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
     </row>
-    <row r="151" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="151" ht="12.75" customHeight="true">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4440,7 +4816,7 @@
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
     </row>
-    <row r="152" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="152" ht="12.75" customHeight="true">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4465,7 +4841,7 @@
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
     </row>
-    <row r="153" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="153" ht="12.75" customHeight="true">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4490,7 +4866,7 @@
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
     </row>
-    <row r="154" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="154" ht="12.75" customHeight="true">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4515,7 +4891,7 @@
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
     </row>
-    <row r="155" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="155" ht="12.75" customHeight="true">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4540,7 +4916,7 @@
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
     </row>
-    <row r="156" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="156" ht="12.75" customHeight="true">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4565,7 +4941,7 @@
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
     </row>
-    <row r="157" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="157" ht="12.75" customHeight="true">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4590,7 +4966,7 @@
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
     </row>
-    <row r="158" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="158" ht="12.75" customHeight="true">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4615,7 +4991,7 @@
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
     </row>
-    <row r="159" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="159" ht="12.75" customHeight="true">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4640,7 +5016,7 @@
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
     </row>
-    <row r="160" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="160" ht="12.75" customHeight="true">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4665,7 +5041,7 @@
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
     </row>
-    <row r="161" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="161" ht="12.75" customHeight="true">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4690,7 +5066,7 @@
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
     </row>
-    <row r="162" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="162" ht="12.75" customHeight="true">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4715,7 +5091,7 @@
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
     </row>
-    <row r="163" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="163" ht="12.75" customHeight="true">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4740,7 +5116,7 @@
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
     </row>
-    <row r="164" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="164" ht="12.75" customHeight="true">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4765,7 +5141,7 @@
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
     </row>
-    <row r="165" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="165" ht="12.75" customHeight="true">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4790,7 +5166,7 @@
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
     </row>
-    <row r="166" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="166" ht="12.75" customHeight="true">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -4815,7 +5191,7 @@
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
     </row>
-    <row r="167" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="167" ht="12.75" customHeight="true">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -4840,7 +5216,7 @@
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
     </row>
-    <row r="168" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="168" ht="12.75" customHeight="true">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -4865,7 +5241,7 @@
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
     </row>
-    <row r="169" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="169" ht="12.75" customHeight="true">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -4890,7 +5266,7 @@
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
     </row>
-    <row r="170" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="170" ht="12.75" customHeight="true">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -4915,7 +5291,7 @@
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
     </row>
-    <row r="171" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="171" ht="12.75" customHeight="true">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -4940,7 +5316,7 @@
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
     </row>
-    <row r="172" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="172" ht="12.75" customHeight="true">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -4965,7 +5341,7 @@
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
     </row>
-    <row r="173" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="173" ht="12.75" customHeight="true">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -4990,7 +5366,7 @@
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
     </row>
-    <row r="174" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="174" ht="12.75" customHeight="true">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5015,7 +5391,7 @@
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
     </row>
-    <row r="175" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="175" ht="12.75" customHeight="true">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5040,7 +5416,7 @@
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
     </row>
-    <row r="176" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="176" ht="12.75" customHeight="true">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5065,7 +5441,7 @@
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
     </row>
-    <row r="177" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="177" ht="12.75" customHeight="true">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5090,7 +5466,7 @@
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
     </row>
-    <row r="178" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="178" ht="12.75" customHeight="true">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5115,7 +5491,7 @@
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
     </row>
-    <row r="179" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="179" ht="12.75" customHeight="true">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5140,7 +5516,7 @@
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
     </row>
-    <row r="180" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="180" ht="12.75" customHeight="true">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5165,7 +5541,7 @@
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
     </row>
-    <row r="181" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="181" ht="12.75" customHeight="true">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5190,7 +5566,7 @@
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
     </row>
-    <row r="182" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="182" ht="12.75" customHeight="true">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5215,7 +5591,7 @@
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
     </row>
-    <row r="183" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="183" ht="12.75" customHeight="true">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5240,7 +5616,7 @@
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
     </row>
-    <row r="184" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="184" ht="12.75" customHeight="true">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5265,7 +5641,7 @@
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
     </row>
-    <row r="185" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="185" ht="12.75" customHeight="true">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5290,7 +5666,7 @@
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
     </row>
-    <row r="186" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="186" ht="12.75" customHeight="true">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5315,7 +5691,7 @@
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
     </row>
-    <row r="187" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="187" ht="12.75" customHeight="true">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5340,7 +5716,7 @@
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
     </row>
-    <row r="188" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="188" ht="12.75" customHeight="true">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5365,7 +5741,7 @@
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
     </row>
-    <row r="189" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="189" ht="12.75" customHeight="true">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5390,7 +5766,7 @@
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
     </row>
-    <row r="190" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="190" ht="12.75" customHeight="true">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5415,7 +5791,7 @@
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
     </row>
-    <row r="191" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="191" ht="12.75" customHeight="true">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5440,7 +5816,7 @@
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
     </row>
-    <row r="192" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="192" ht="12.75" customHeight="true">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5465,7 +5841,7 @@
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
     </row>
-    <row r="193" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="193" ht="12.75" customHeight="true">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5490,7 +5866,7 @@
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
     </row>
-    <row r="194" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="194" ht="12.75" customHeight="true">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5515,7 +5891,7 @@
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
     </row>
-    <row r="195" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="195" ht="12.75" customHeight="true">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5540,7 +5916,7 @@
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
     </row>
-    <row r="196" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="196" ht="12.75" customHeight="true">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5565,7 +5941,7 @@
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
     </row>
-    <row r="197" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="197" ht="12.75" customHeight="true">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5590,7 +5966,7 @@
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
     </row>
-    <row r="198" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="198" ht="12.75" customHeight="true">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -5615,7 +5991,7 @@
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
     </row>
-    <row r="199" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="199" ht="12.75" customHeight="true">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5640,7 +6016,7 @@
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
     </row>
-    <row r="200" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="200" ht="12.75" customHeight="true">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -5665,7 +6041,7 @@
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
     </row>
-    <row r="201" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="201" ht="12.75" customHeight="true">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -5690,7 +6066,7 @@
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
     </row>
-    <row r="202" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="202" ht="12.75" customHeight="true">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -5715,7 +6091,7 @@
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
     </row>
-    <row r="203" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="203" ht="12.75" customHeight="true">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -5740,7 +6116,7 @@
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
     </row>
-    <row r="204" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="204" ht="12.75" customHeight="true">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -5765,7 +6141,7 @@
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
     </row>
-    <row r="205" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="205" ht="12.75" customHeight="true">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -5790,7 +6166,7 @@
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
     </row>
-    <row r="206" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="206" ht="12.75" customHeight="true">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -5815,7 +6191,7 @@
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
     </row>
-    <row r="207" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="207" ht="12.75" customHeight="true">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -5840,7 +6216,7 @@
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
     </row>
-    <row r="208" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="208" ht="12.75" customHeight="true">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -5865,7 +6241,7 @@
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
     </row>
-    <row r="209" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="209" ht="12.75" customHeight="true">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -5890,7 +6266,7 @@
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
     </row>
-    <row r="210" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="210" ht="12.75" customHeight="true">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -5915,7 +6291,7 @@
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
     </row>
-    <row r="211" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="211" ht="12.75" customHeight="true">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -5940,7 +6316,7 @@
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
     </row>
-    <row r="212" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="212" ht="12.75" customHeight="true">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -5965,7 +6341,7 @@
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
     </row>
-    <row r="213" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="213" ht="12.75" customHeight="true">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -5990,7 +6366,7 @@
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
     </row>
-    <row r="214" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="214" ht="12.75" customHeight="true">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -6015,7 +6391,7 @@
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
     </row>
-    <row r="215" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="215" ht="12.75" customHeight="true">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -6040,7 +6416,7 @@
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
     </row>
-    <row r="216" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="216" ht="12.75" customHeight="true">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -6065,7 +6441,7 @@
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
     </row>
-    <row r="217" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="217" ht="12.75" customHeight="true">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -6090,7 +6466,7 @@
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
     </row>
-    <row r="218" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="218" ht="12.75" customHeight="true">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -6115,7 +6491,7 @@
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
     </row>
-    <row r="219" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="219" ht="12.75" customHeight="true">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -6140,7 +6516,7 @@
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
     </row>
-    <row r="220" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="220" ht="12.75" customHeight="true">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -6165,7 +6541,7 @@
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
     </row>
-    <row r="221" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="221" ht="12.75" customHeight="true">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -6190,7 +6566,7 @@
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
     </row>
-    <row r="222" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="222" ht="12.75" customHeight="true">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -6215,7 +6591,7 @@
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
     </row>
-    <row r="223" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="223" ht="12.75" customHeight="true">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -6240,7 +6616,7 @@
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
     </row>
-    <row r="224" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="224" ht="12.75" customHeight="true">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -6265,7 +6641,7 @@
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
     </row>
-    <row r="225" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="225" ht="12.75" customHeight="true">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -6290,7 +6666,7 @@
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
     </row>
-    <row r="226" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="226" ht="12.75" customHeight="true">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -6315,7 +6691,7 @@
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
     </row>
-    <row r="227" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="227" ht="12.75" customHeight="true">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -6340,7 +6716,7 @@
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
     </row>
-    <row r="228" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="228" ht="12.75" customHeight="true">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -6365,7 +6741,7 @@
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
     </row>
-    <row r="229" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="229" ht="12.75" customHeight="true">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -6390,7 +6766,7 @@
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
     </row>
-    <row r="230" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="230" ht="12.75" customHeight="true">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -6415,7 +6791,7 @@
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
     </row>
-    <row r="231" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="231" ht="12.75" customHeight="true">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -6440,7 +6816,7 @@
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
     </row>
-    <row r="232" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="232" ht="12.75" customHeight="true">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -6465,7 +6841,7 @@
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
     </row>
-    <row r="233" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="233" ht="12.75" customHeight="true">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -6490,7 +6866,7 @@
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
     </row>
-    <row r="234" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="234" ht="12.75" customHeight="true">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -6515,7 +6891,7 @@
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
     </row>
-    <row r="235" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="235" ht="12.75" customHeight="true">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -6540,7 +6916,7 @@
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
     </row>
-    <row r="236" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="236" ht="12.75" customHeight="true">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -6565,7 +6941,7 @@
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
     </row>
-    <row r="237" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="237" ht="12.75" customHeight="true">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -6590,7 +6966,7 @@
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
     </row>
-    <row r="238" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="238" ht="12.75" customHeight="true">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -6615,7 +6991,7 @@
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
     </row>
-    <row r="239" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="239" ht="12.75" customHeight="true">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -6640,7 +7016,7 @@
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
     </row>
-    <row r="240" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="240" ht="12.75" customHeight="true">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -6665,7 +7041,7 @@
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
     </row>
-    <row r="241" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="241" ht="12.75" customHeight="true">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -6690,7 +7066,7 @@
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
     </row>
-    <row r="242" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="242" ht="12.75" customHeight="true">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -6715,7 +7091,7 @@
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
     </row>
-    <row r="243" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="243" ht="12.75" customHeight="true">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -6740,7 +7116,7 @@
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
     </row>
-    <row r="244" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="244" ht="12.75" customHeight="true">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -6765,7 +7141,7 @@
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
     </row>
-    <row r="245" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="245" ht="12.75" customHeight="true">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -6790,7 +7166,7 @@
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
     </row>
-    <row r="246" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="246" ht="12.75" customHeight="true">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -6815,7 +7191,7 @@
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
     </row>
-    <row r="247" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="247" ht="12.75" customHeight="true">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -6840,7 +7216,7 @@
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
     </row>
-    <row r="248" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="248" ht="12.75" customHeight="true">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -6865,7 +7241,7 @@
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
     </row>
-    <row r="249" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="249" ht="12.75" customHeight="true">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -6890,7 +7266,7 @@
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
     </row>
-    <row r="250" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="250" ht="12.75" customHeight="true">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -6915,7 +7291,7 @@
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
     </row>
-    <row r="251" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="251" ht="12.75" customHeight="true">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -6940,7 +7316,7 @@
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
     </row>
-    <row r="252" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="252" ht="12.75" customHeight="true">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -6965,7 +7341,7 @@
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
     </row>
-    <row r="253" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="253" ht="12.75" customHeight="true">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -6990,7 +7366,7 @@
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
     </row>
-    <row r="254" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="254" ht="12.75" customHeight="true">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -7015,7 +7391,7 @@
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
     </row>
-    <row r="255" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="255" ht="12.75" customHeight="true">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -7040,7 +7416,7 @@
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
     </row>
-    <row r="256" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="256" ht="12.75" customHeight="true">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -7065,7 +7441,7 @@
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
     </row>
-    <row r="257" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="257" ht="12.75" customHeight="true">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -7090,7 +7466,7 @@
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
     </row>
-    <row r="258" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="258" ht="12.75" customHeight="true">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -7115,7 +7491,7 @@
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
     </row>
-    <row r="259" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="259" ht="12.75" customHeight="true">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -7140,7 +7516,7 @@
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
     </row>
-    <row r="260" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="260" ht="12.75" customHeight="true">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -7165,7 +7541,7 @@
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
     </row>
-    <row r="261" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="261" ht="12.75" customHeight="true">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -7190,7 +7566,7 @@
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
     </row>
-    <row r="262" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="262" ht="12.75" customHeight="true">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -7215,7 +7591,7 @@
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
     </row>
-    <row r="263" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="263" ht="12.75" customHeight="true">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -7240,7 +7616,7 @@
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
     </row>
-    <row r="264" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="264" ht="12.75" customHeight="true">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -7265,7 +7641,7 @@
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
     </row>
-    <row r="265" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="265" ht="12.75" customHeight="true">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -7290,7 +7666,7 @@
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
     </row>
-    <row r="266" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="266" ht="12.75" customHeight="true">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -7315,7 +7691,7 @@
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
     </row>
-    <row r="267" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="267" ht="12.75" customHeight="true">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -7340,7 +7716,7 @@
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
     </row>
-    <row r="268" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="268" ht="12.75" customHeight="true">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -7365,7 +7741,7 @@
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
     </row>
-    <row r="269" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="269" ht="12.75" customHeight="true">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -7390,7 +7766,7 @@
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
     </row>
-    <row r="270" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="270" ht="12.75" customHeight="true">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -7415,7 +7791,7 @@
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
     </row>
-    <row r="271" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="271" ht="12.75" customHeight="true">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -7440,7 +7816,7 @@
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
     </row>
-    <row r="272" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="272" ht="12.75" customHeight="true">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -7465,7 +7841,7 @@
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
     </row>
-    <row r="273" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="273" ht="12.75" customHeight="true">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -7490,7 +7866,7 @@
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
     </row>
-    <row r="274" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="274" ht="12.75" customHeight="true">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -7515,7 +7891,7 @@
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
     </row>
-    <row r="275" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="275" ht="12.75" customHeight="true">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -7540,7 +7916,7 @@
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
     </row>
-    <row r="276" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="276" ht="12.75" customHeight="true">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -7565,7 +7941,7 @@
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
     </row>
-    <row r="277" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="277" ht="12.75" customHeight="true">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -7590,7 +7966,7 @@
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
     </row>
-    <row r="278" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="278" ht="12.75" customHeight="true">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -7615,7 +7991,7 @@
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
     </row>
-    <row r="279" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="279" ht="12.75" customHeight="true">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -7640,7 +8016,7 @@
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
     </row>
-    <row r="280" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="280" ht="12.75" customHeight="true">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -7665,7 +8041,7 @@
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
     </row>
-    <row r="281" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="281" ht="12.75" customHeight="true">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -7690,7 +8066,7 @@
       <c r="V281" s="1"/>
       <c r="W281" s="1"/>
     </row>
-    <row r="282" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="282" ht="12.75" customHeight="true">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -7715,7 +8091,7 @@
       <c r="V282" s="1"/>
       <c r="W282" s="1"/>
     </row>
-    <row r="283" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="283" ht="12.75" customHeight="true">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -7740,7 +8116,7 @@
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
     </row>
-    <row r="284" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="284" ht="12.75" customHeight="true">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -7765,7 +8141,7 @@
       <c r="V284" s="1"/>
       <c r="W284" s="1"/>
     </row>
-    <row r="285" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="285" ht="12.75" customHeight="true">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -7790,7 +8166,7 @@
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
     </row>
-    <row r="286" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="286" ht="12.75" customHeight="true">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -7815,7 +8191,7 @@
       <c r="V286" s="1"/>
       <c r="W286" s="1"/>
     </row>
-    <row r="287" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="287" ht="12.75" customHeight="true">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -7840,7 +8216,7 @@
       <c r="V287" s="1"/>
       <c r="W287" s="1"/>
     </row>
-    <row r="288" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="288" ht="12.75" customHeight="true">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -7865,7 +8241,7 @@
       <c r="V288" s="1"/>
       <c r="W288" s="1"/>
     </row>
-    <row r="289" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="289" ht="12.75" customHeight="true">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -7890,7 +8266,7 @@
       <c r="V289" s="1"/>
       <c r="W289" s="1"/>
     </row>
-    <row r="290" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="290" ht="12.75" customHeight="true">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -7915,7 +8291,7 @@
       <c r="V290" s="1"/>
       <c r="W290" s="1"/>
     </row>
-    <row r="291" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="291" ht="12.75" customHeight="true">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -7940,7 +8316,7 @@
       <c r="V291" s="1"/>
       <c r="W291" s="1"/>
     </row>
-    <row r="292" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="292" ht="12.75" customHeight="true">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -7965,7 +8341,7 @@
       <c r="V292" s="1"/>
       <c r="W292" s="1"/>
     </row>
-    <row r="293" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="293" ht="12.75" customHeight="true">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -7990,7 +8366,7 @@
       <c r="V293" s="1"/>
       <c r="W293" s="1"/>
     </row>
-    <row r="294" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="294" ht="12.75" customHeight="true">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -8015,7 +8391,7 @@
       <c r="V294" s="1"/>
       <c r="W294" s="1"/>
     </row>
-    <row r="295" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="295" ht="12.75" customHeight="true">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -8040,7 +8416,7 @@
       <c r="V295" s="1"/>
       <c r="W295" s="1"/>
     </row>
-    <row r="296" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="296" ht="12.75" customHeight="true">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -8065,7 +8441,7 @@
       <c r="V296" s="1"/>
       <c r="W296" s="1"/>
     </row>
-    <row r="297" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="297" ht="12.75" customHeight="true">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -8090,7 +8466,7 @@
       <c r="V297" s="1"/>
       <c r="W297" s="1"/>
     </row>
-    <row r="298" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="298" ht="12.75" customHeight="true">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -8115,7 +8491,7 @@
       <c r="V298" s="1"/>
       <c r="W298" s="1"/>
     </row>
-    <row r="299" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="299" ht="12.75" customHeight="true">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -8140,7 +8516,7 @@
       <c r="V299" s="1"/>
       <c r="W299" s="1"/>
     </row>
-    <row r="300" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="300" ht="12.75" customHeight="true">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -8165,7 +8541,7 @@
       <c r="V300" s="1"/>
       <c r="W300" s="1"/>
     </row>
-    <row r="301" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="301" ht="12.75" customHeight="true">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -8190,7 +8566,7 @@
       <c r="V301" s="1"/>
       <c r="W301" s="1"/>
     </row>
-    <row r="302" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="302" ht="12.75" customHeight="true">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -8215,7 +8591,7 @@
       <c r="V302" s="1"/>
       <c r="W302" s="1"/>
     </row>
-    <row r="303" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="303" ht="12.75" customHeight="true">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -8240,7 +8616,7 @@
       <c r="V303" s="1"/>
       <c r="W303" s="1"/>
     </row>
-    <row r="304" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="304" ht="12.75" customHeight="true">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -8265,7 +8641,7 @@
       <c r="V304" s="1"/>
       <c r="W304" s="1"/>
     </row>
-    <row r="305" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="305" ht="12.75" customHeight="true">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -8290,7 +8666,7 @@
       <c r="V305" s="1"/>
       <c r="W305" s="1"/>
     </row>
-    <row r="306" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="306" ht="12.75" customHeight="true">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -8315,7 +8691,7 @@
       <c r="V306" s="1"/>
       <c r="W306" s="1"/>
     </row>
-    <row r="307" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="307" ht="12.75" customHeight="true">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -8340,7 +8716,7 @@
       <c r="V307" s="1"/>
       <c r="W307" s="1"/>
     </row>
-    <row r="308" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="308" ht="12.75" customHeight="true">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -8365,7 +8741,7 @@
       <c r="V308" s="1"/>
       <c r="W308" s="1"/>
     </row>
-    <row r="309" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="309" ht="12.75" customHeight="true">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -8390,7 +8766,7 @@
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
     </row>
-    <row r="310" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="310" ht="12.75" customHeight="true">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -8415,7 +8791,7 @@
       <c r="V310" s="1"/>
       <c r="W310" s="1"/>
     </row>
-    <row r="311" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="311" ht="12.75" customHeight="true">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -8440,7 +8816,7 @@
       <c r="V311" s="1"/>
       <c r="W311" s="1"/>
     </row>
-    <row r="312" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="312" ht="12.75" customHeight="true">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -8465,7 +8841,7 @@
       <c r="V312" s="1"/>
       <c r="W312" s="1"/>
     </row>
-    <row r="313" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="313" ht="12.75" customHeight="true">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -8490,7 +8866,7 @@
       <c r="V313" s="1"/>
       <c r="W313" s="1"/>
     </row>
-    <row r="314" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="314" ht="12.75" customHeight="true">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -8515,7 +8891,7 @@
       <c r="V314" s="1"/>
       <c r="W314" s="1"/>
     </row>
-    <row r="315" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="315" ht="12.75" customHeight="true">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -8540,7 +8916,7 @@
       <c r="V315" s="1"/>
       <c r="W315" s="1"/>
     </row>
-    <row r="316" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="316" ht="12.75" customHeight="true">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -8565,7 +8941,7 @@
       <c r="V316" s="1"/>
       <c r="W316" s="1"/>
     </row>
-    <row r="317" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="317" ht="12.75" customHeight="true">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -8590,7 +8966,7 @@
       <c r="V317" s="1"/>
       <c r="W317" s="1"/>
     </row>
-    <row r="318" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="318" ht="12.75" customHeight="true">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -8615,7 +8991,7 @@
       <c r="V318" s="1"/>
       <c r="W318" s="1"/>
     </row>
-    <row r="319" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="319" ht="12.75" customHeight="true">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -8640,7 +9016,7 @@
       <c r="V319" s="1"/>
       <c r="W319" s="1"/>
     </row>
-    <row r="320" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="320" ht="12.75" customHeight="true">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -8665,7 +9041,7 @@
       <c r="V320" s="1"/>
       <c r="W320" s="1"/>
     </row>
-    <row r="321" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="321" ht="12.75" customHeight="true">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -8690,7 +9066,7 @@
       <c r="V321" s="1"/>
       <c r="W321" s="1"/>
     </row>
-    <row r="322" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="322" ht="12.75" customHeight="true">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -8715,7 +9091,7 @@
       <c r="V322" s="1"/>
       <c r="W322" s="1"/>
     </row>
-    <row r="323" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="323" ht="12.75" customHeight="true">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -8740,7 +9116,7 @@
       <c r="V323" s="1"/>
       <c r="W323" s="1"/>
     </row>
-    <row r="324" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="324" ht="12.75" customHeight="true">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -8765,7 +9141,7 @@
       <c r="V324" s="1"/>
       <c r="W324" s="1"/>
     </row>
-    <row r="325" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="325" ht="12.75" customHeight="true">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -8790,7 +9166,7 @@
       <c r="V325" s="1"/>
       <c r="W325" s="1"/>
     </row>
-    <row r="326" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="326" ht="12.75" customHeight="true">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -8815,7 +9191,7 @@
       <c r="V326" s="1"/>
       <c r="W326" s="1"/>
     </row>
-    <row r="327" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="327" ht="12.75" customHeight="true">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -8840,7 +9216,7 @@
       <c r="V327" s="1"/>
       <c r="W327" s="1"/>
     </row>
-    <row r="328" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="328" ht="12.75" customHeight="true">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -8865,7 +9241,7 @@
       <c r="V328" s="1"/>
       <c r="W328" s="1"/>
     </row>
-    <row r="329" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="329" ht="12.75" customHeight="true">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -8890,7 +9266,7 @@
       <c r="V329" s="1"/>
       <c r="W329" s="1"/>
     </row>
-    <row r="330" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="330" ht="12.75" customHeight="true">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -8915,7 +9291,7 @@
       <c r="V330" s="1"/>
       <c r="W330" s="1"/>
     </row>
-    <row r="331" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="331" ht="12.75" customHeight="true">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -8940,7 +9316,7 @@
       <c r="V331" s="1"/>
       <c r="W331" s="1"/>
     </row>
-    <row r="332" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="332" ht="12.75" customHeight="true">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -8965,7 +9341,7 @@
       <c r="V332" s="1"/>
       <c r="W332" s="1"/>
     </row>
-    <row r="333" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="333" ht="12.75" customHeight="true">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -8990,7 +9366,7 @@
       <c r="V333" s="1"/>
       <c r="W333" s="1"/>
     </row>
-    <row r="334" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="334" ht="12.75" customHeight="true">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -9015,7 +9391,7 @@
       <c r="V334" s="1"/>
       <c r="W334" s="1"/>
     </row>
-    <row r="335" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="335" ht="12.75" customHeight="true">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -9040,7 +9416,7 @@
       <c r="V335" s="1"/>
       <c r="W335" s="1"/>
     </row>
-    <row r="336" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="336" ht="12.75" customHeight="true">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -9065,7 +9441,7 @@
       <c r="V336" s="1"/>
       <c r="W336" s="1"/>
     </row>
-    <row r="337" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="337" ht="12.75" customHeight="true">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -9090,7 +9466,7 @@
       <c r="V337" s="1"/>
       <c r="W337" s="1"/>
     </row>
-    <row r="338" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="338" ht="12.75" customHeight="true">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -9115,7 +9491,7 @@
       <c r="V338" s="1"/>
       <c r="W338" s="1"/>
     </row>
-    <row r="339" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="339" ht="12.75" customHeight="true">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -9140,7 +9516,7 @@
       <c r="V339" s="1"/>
       <c r="W339" s="1"/>
     </row>
-    <row r="340" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="340" ht="12.75" customHeight="true">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -9165,7 +9541,7 @@
       <c r="V340" s="1"/>
       <c r="W340" s="1"/>
     </row>
-    <row r="341" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="341" ht="12.75" customHeight="true">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -9190,7 +9566,7 @@
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
     </row>
-    <row r="342" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="342" ht="12.75" customHeight="true">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -9215,7 +9591,7 @@
       <c r="V342" s="1"/>
       <c r="W342" s="1"/>
     </row>
-    <row r="343" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="343" ht="12.75" customHeight="true">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -9240,7 +9616,7 @@
       <c r="V343" s="1"/>
       <c r="W343" s="1"/>
     </row>
-    <row r="344" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="344" ht="12.75" customHeight="true">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -9265,7 +9641,7 @@
       <c r="V344" s="1"/>
       <c r="W344" s="1"/>
     </row>
-    <row r="345" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="345" ht="12.75" customHeight="true">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -9290,7 +9666,7 @@
       <c r="V345" s="1"/>
       <c r="W345" s="1"/>
     </row>
-    <row r="346" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="346" ht="12.75" customHeight="true">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -9315,7 +9691,7 @@
       <c r="V346" s="1"/>
       <c r="W346" s="1"/>
     </row>
-    <row r="347" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="347" ht="12.75" customHeight="true">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -9340,7 +9716,7 @@
       <c r="V347" s="1"/>
       <c r="W347" s="1"/>
     </row>
-    <row r="348" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="348" ht="12.75" customHeight="true">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -9365,7 +9741,7 @@
       <c r="V348" s="1"/>
       <c r="W348" s="1"/>
     </row>
-    <row r="349" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="349" ht="12.75" customHeight="true">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -9390,7 +9766,7 @@
       <c r="V349" s="1"/>
       <c r="W349" s="1"/>
     </row>
-    <row r="350" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="350" ht="12.75" customHeight="true">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -9415,7 +9791,7 @@
       <c r="V350" s="1"/>
       <c r="W350" s="1"/>
     </row>
-    <row r="351" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="351" ht="12.75" customHeight="true">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -9440,7 +9816,7 @@
       <c r="V351" s="1"/>
       <c r="W351" s="1"/>
     </row>
-    <row r="352" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="352" ht="12.75" customHeight="true">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -9465,7 +9841,7 @@
       <c r="V352" s="1"/>
       <c r="W352" s="1"/>
     </row>
-    <row r="353" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="353" ht="12.75" customHeight="true">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -9490,7 +9866,7 @@
       <c r="V353" s="1"/>
       <c r="W353" s="1"/>
     </row>
-    <row r="354" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="354" ht="12.75" customHeight="true">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -9515,7 +9891,7 @@
       <c r="V354" s="1"/>
       <c r="W354" s="1"/>
     </row>
-    <row r="355" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="355" ht="12.75" customHeight="true">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -9540,7 +9916,7 @@
       <c r="V355" s="1"/>
       <c r="W355" s="1"/>
     </row>
-    <row r="356" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="356" ht="12.75" customHeight="true">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -9565,7 +9941,7 @@
       <c r="V356" s="1"/>
       <c r="W356" s="1"/>
     </row>
-    <row r="357" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="357" ht="12.75" customHeight="true">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -9590,7 +9966,7 @@
       <c r="V357" s="1"/>
       <c r="W357" s="1"/>
     </row>
-    <row r="358" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="358" ht="12.75" customHeight="true">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -9615,7 +9991,7 @@
       <c r="V358" s="1"/>
       <c r="W358" s="1"/>
     </row>
-    <row r="359" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="359" ht="12.75" customHeight="true">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -9640,7 +10016,7 @@
       <c r="V359" s="1"/>
       <c r="W359" s="1"/>
     </row>
-    <row r="360" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="360" ht="12.75" customHeight="true">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -9665,7 +10041,7 @@
       <c r="V360" s="1"/>
       <c r="W360" s="1"/>
     </row>
-    <row r="361" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="361" ht="12.75" customHeight="true">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -9690,7 +10066,7 @@
       <c r="V361" s="1"/>
       <c r="W361" s="1"/>
     </row>
-    <row r="362" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="362" ht="12.75" customHeight="true">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -9715,7 +10091,7 @@
       <c r="V362" s="1"/>
       <c r="W362" s="1"/>
     </row>
-    <row r="363" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="363" ht="12.75" customHeight="true">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -9740,7 +10116,7 @@
       <c r="V363" s="1"/>
       <c r="W363" s="1"/>
     </row>
-    <row r="364" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="364" ht="12.75" customHeight="true">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -9765,7 +10141,7 @@
       <c r="V364" s="1"/>
       <c r="W364" s="1"/>
     </row>
-    <row r="365" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="365" ht="12.75" customHeight="true">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -9790,7 +10166,7 @@
       <c r="V365" s="1"/>
       <c r="W365" s="1"/>
     </row>
-    <row r="366" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="366" ht="12.75" customHeight="true">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -9815,7 +10191,7 @@
       <c r="V366" s="1"/>
       <c r="W366" s="1"/>
     </row>
-    <row r="367" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="367" ht="12.75" customHeight="true">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -9840,7 +10216,7 @@
       <c r="V367" s="1"/>
       <c r="W367" s="1"/>
     </row>
-    <row r="368" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="368" ht="12.75" customHeight="true">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -9865,7 +10241,7 @@
       <c r="V368" s="1"/>
       <c r="W368" s="1"/>
     </row>
-    <row r="369" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="369" ht="12.75" customHeight="true">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -9890,7 +10266,7 @@
       <c r="V369" s="1"/>
       <c r="W369" s="1"/>
     </row>
-    <row r="370" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="370" ht="12.75" customHeight="true">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -9915,7 +10291,7 @@
       <c r="V370" s="1"/>
       <c r="W370" s="1"/>
     </row>
-    <row r="371" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="371" ht="12.75" customHeight="true">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -9940,7 +10316,7 @@
       <c r="V371" s="1"/>
       <c r="W371" s="1"/>
     </row>
-    <row r="372" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="372" ht="12.75" customHeight="true">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -9965,7 +10341,7 @@
       <c r="V372" s="1"/>
       <c r="W372" s="1"/>
     </row>
-    <row r="373" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="373" ht="12.75" customHeight="true">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -9990,7 +10366,7 @@
       <c r="V373" s="1"/>
       <c r="W373" s="1"/>
     </row>
-    <row r="374" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="374" ht="12.75" customHeight="true">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -10015,7 +10391,7 @@
       <c r="V374" s="1"/>
       <c r="W374" s="1"/>
     </row>
-    <row r="375" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="375" ht="12.75" customHeight="true">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -10040,7 +10416,7 @@
       <c r="V375" s="1"/>
       <c r="W375" s="1"/>
     </row>
-    <row r="376" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="376" ht="12.75" customHeight="true">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -10065,7 +10441,7 @@
       <c r="V376" s="1"/>
       <c r="W376" s="1"/>
     </row>
-    <row r="377" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="377" ht="12.75" customHeight="true">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -10090,7 +10466,7 @@
       <c r="V377" s="1"/>
       <c r="W377" s="1"/>
     </row>
-    <row r="378" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="378" ht="12.75" customHeight="true">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -10115,7 +10491,7 @@
       <c r="V378" s="1"/>
       <c r="W378" s="1"/>
     </row>
-    <row r="379" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="379" ht="12.75" customHeight="true">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -10140,7 +10516,7 @@
       <c r="V379" s="1"/>
       <c r="W379" s="1"/>
     </row>
-    <row r="380" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="380" ht="12.75" customHeight="true">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -10165,7 +10541,7 @@
       <c r="V380" s="1"/>
       <c r="W380" s="1"/>
     </row>
-    <row r="381" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="381" ht="12.75" customHeight="true">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -10190,7 +10566,7 @@
       <c r="V381" s="1"/>
       <c r="W381" s="1"/>
     </row>
-    <row r="382" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="382" ht="12.75" customHeight="true">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -10215,7 +10591,7 @@
       <c r="V382" s="1"/>
       <c r="W382" s="1"/>
     </row>
-    <row r="383" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="383" ht="12.75" customHeight="true">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -10240,7 +10616,7 @@
       <c r="V383" s="1"/>
       <c r="W383" s="1"/>
     </row>
-    <row r="384" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="384" ht="12.75" customHeight="true">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -10265,7 +10641,7 @@
       <c r="V384" s="1"/>
       <c r="W384" s="1"/>
     </row>
-    <row r="385" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="385" ht="12.75" customHeight="true">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -10290,7 +10666,7 @@
       <c r="V385" s="1"/>
       <c r="W385" s="1"/>
     </row>
-    <row r="386" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="386" ht="12.75" customHeight="true">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -10315,7 +10691,7 @@
       <c r="V386" s="1"/>
       <c r="W386" s="1"/>
     </row>
-    <row r="387" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="387" ht="12.75" customHeight="true">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -10340,7 +10716,7 @@
       <c r="V387" s="1"/>
       <c r="W387" s="1"/>
     </row>
-    <row r="388" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="388" ht="12.75" customHeight="true">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -10365,7 +10741,7 @@
       <c r="V388" s="1"/>
       <c r="W388" s="1"/>
     </row>
-    <row r="389" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="389" ht="12.75" customHeight="true">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -10390,7 +10766,7 @@
       <c r="V389" s="1"/>
       <c r="W389" s="1"/>
     </row>
-    <row r="390" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="390" ht="12.75" customHeight="true">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -10415,7 +10791,7 @@
       <c r="V390" s="1"/>
       <c r="W390" s="1"/>
     </row>
-    <row r="391" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="391" ht="12.75" customHeight="true">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -10440,7 +10816,7 @@
       <c r="V391" s="1"/>
       <c r="W391" s="1"/>
     </row>
-    <row r="392" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="392" ht="12.75" customHeight="true">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -10465,7 +10841,7 @@
       <c r="V392" s="1"/>
       <c r="W392" s="1"/>
     </row>
-    <row r="393" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="393" ht="12.75" customHeight="true">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -10490,7 +10866,7 @@
       <c r="V393" s="1"/>
       <c r="W393" s="1"/>
     </row>
-    <row r="394" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="394" ht="12.75" customHeight="true">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -10515,7 +10891,7 @@
       <c r="V394" s="1"/>
       <c r="W394" s="1"/>
     </row>
-    <row r="395" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="395" ht="12.75" customHeight="true">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -10540,7 +10916,7 @@
       <c r="V395" s="1"/>
       <c r="W395" s="1"/>
     </row>
-    <row r="396" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="396" ht="12.75" customHeight="true">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -10565,7 +10941,7 @@
       <c r="V396" s="1"/>
       <c r="W396" s="1"/>
     </row>
-    <row r="397" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="397" ht="12.75" customHeight="true">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -10590,7 +10966,7 @@
       <c r="V397" s="1"/>
       <c r="W397" s="1"/>
     </row>
-    <row r="398" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="398" ht="12.75" customHeight="true">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -10615,7 +10991,7 @@
       <c r="V398" s="1"/>
       <c r="W398" s="1"/>
     </row>
-    <row r="399" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="399" ht="12.75" customHeight="true">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -10640,7 +11016,7 @@
       <c r="V399" s="1"/>
       <c r="W399" s="1"/>
     </row>
-    <row r="400" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="400" ht="12.75" customHeight="true">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -10665,7 +11041,7 @@
       <c r="V400" s="1"/>
       <c r="W400" s="1"/>
     </row>
-    <row r="401" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="401" ht="12.75" customHeight="true">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -10690,7 +11066,7 @@
       <c r="V401" s="1"/>
       <c r="W401" s="1"/>
     </row>
-    <row r="402" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="402" ht="12.75" customHeight="true">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -10715,7 +11091,7 @@
       <c r="V402" s="1"/>
       <c r="W402" s="1"/>
     </row>
-    <row r="403" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="403" ht="12.75" customHeight="true">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -10740,7 +11116,7 @@
       <c r="V403" s="1"/>
       <c r="W403" s="1"/>
     </row>
-    <row r="404" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="404" ht="12.75" customHeight="true">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -10765,7 +11141,7 @@
       <c r="V404" s="1"/>
       <c r="W404" s="1"/>
     </row>
-    <row r="405" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="405" ht="12.75" customHeight="true">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -10790,7 +11166,7 @@
       <c r="V405" s="1"/>
       <c r="W405" s="1"/>
     </row>
-    <row r="406" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="406" ht="12.75" customHeight="true">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -10815,7 +11191,7 @@
       <c r="V406" s="1"/>
       <c r="W406" s="1"/>
     </row>
-    <row r="407" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="407" ht="12.75" customHeight="true">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -10840,7 +11216,7 @@
       <c r="V407" s="1"/>
       <c r="W407" s="1"/>
     </row>
-    <row r="408" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="408" ht="12.75" customHeight="true">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -10865,7 +11241,7 @@
       <c r="V408" s="1"/>
       <c r="W408" s="1"/>
     </row>
-    <row r="409" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="409" ht="12.75" customHeight="true">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -10890,7 +11266,7 @@
       <c r="V409" s="1"/>
       <c r="W409" s="1"/>
     </row>
-    <row r="410" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="410" ht="12.75" customHeight="true">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -10915,7 +11291,7 @@
       <c r="V410" s="1"/>
       <c r="W410" s="1"/>
     </row>
-    <row r="411" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="411" ht="12.75" customHeight="true">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -10940,7 +11316,7 @@
       <c r="V411" s="1"/>
       <c r="W411" s="1"/>
     </row>
-    <row r="412" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="412" ht="12.75" customHeight="true">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -10965,7 +11341,7 @@
       <c r="V412" s="1"/>
       <c r="W412" s="1"/>
     </row>
-    <row r="413" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="413" ht="12.75" customHeight="true">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -10990,7 +11366,7 @@
       <c r="V413" s="1"/>
       <c r="W413" s="1"/>
     </row>
-    <row r="414" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="414" ht="12.75" customHeight="true">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -11015,7 +11391,7 @@
       <c r="V414" s="1"/>
       <c r="W414" s="1"/>
     </row>
-    <row r="415" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="415" ht="12.75" customHeight="true">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -11040,7 +11416,7 @@
       <c r="V415" s="1"/>
       <c r="W415" s="1"/>
     </row>
-    <row r="416" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="416" ht="12.75" customHeight="true">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -11065,7 +11441,7 @@
       <c r="V416" s="1"/>
       <c r="W416" s="1"/>
     </row>
-    <row r="417" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="417" ht="12.75" customHeight="true">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -11090,7 +11466,7 @@
       <c r="V417" s="1"/>
       <c r="W417" s="1"/>
     </row>
-    <row r="418" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="418" ht="12.75" customHeight="true">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -11115,7 +11491,7 @@
       <c r="V418" s="1"/>
       <c r="W418" s="1"/>
     </row>
-    <row r="419" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="419" ht="12.75" customHeight="true">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -11140,7 +11516,7 @@
       <c r="V419" s="1"/>
       <c r="W419" s="1"/>
     </row>
-    <row r="420" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="420" ht="12.75" customHeight="true">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -11165,7 +11541,7 @@
       <c r="V420" s="1"/>
       <c r="W420" s="1"/>
     </row>
-    <row r="421" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="421" ht="12.75" customHeight="true">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -11190,7 +11566,7 @@
       <c r="V421" s="1"/>
       <c r="W421" s="1"/>
     </row>
-    <row r="422" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="422" ht="12.75" customHeight="true">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -11215,7 +11591,7 @@
       <c r="V422" s="1"/>
       <c r="W422" s="1"/>
     </row>
-    <row r="423" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="423" ht="12.75" customHeight="true">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -11240,7 +11616,7 @@
       <c r="V423" s="1"/>
       <c r="W423" s="1"/>
     </row>
-    <row r="424" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="424" ht="12.75" customHeight="true">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -11265,7 +11641,7 @@
       <c r="V424" s="1"/>
       <c r="W424" s="1"/>
     </row>
-    <row r="425" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="425" ht="12.75" customHeight="true">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -11290,7 +11666,7 @@
       <c r="V425" s="1"/>
       <c r="W425" s="1"/>
     </row>
-    <row r="426" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="426" ht="12.75" customHeight="true">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -11315,7 +11691,7 @@
       <c r="V426" s="1"/>
       <c r="W426" s="1"/>
     </row>
-    <row r="427" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="427" ht="12.75" customHeight="true">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -11340,7 +11716,7 @@
       <c r="V427" s="1"/>
       <c r="W427" s="1"/>
     </row>
-    <row r="428" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="428" ht="12.75" customHeight="true">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -11365,7 +11741,7 @@
       <c r="V428" s="1"/>
       <c r="W428" s="1"/>
     </row>
-    <row r="429" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="429" ht="12.75" customHeight="true">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -11390,7 +11766,7 @@
       <c r="V429" s="1"/>
       <c r="W429" s="1"/>
     </row>
-    <row r="430" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="430" ht="12.75" customHeight="true">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -11415,7 +11791,7 @@
       <c r="V430" s="1"/>
       <c r="W430" s="1"/>
     </row>
-    <row r="431" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="431" ht="12.75" customHeight="true">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -11440,7 +11816,7 @@
       <c r="V431" s="1"/>
       <c r="W431" s="1"/>
     </row>
-    <row r="432" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="432" ht="12.75" customHeight="true">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -11465,7 +11841,7 @@
       <c r="V432" s="1"/>
       <c r="W432" s="1"/>
     </row>
-    <row r="433" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="433" ht="12.75" customHeight="true">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -11490,7 +11866,7 @@
       <c r="V433" s="1"/>
       <c r="W433" s="1"/>
     </row>
-    <row r="434" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="434" ht="12.75" customHeight="true">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -11515,7 +11891,7 @@
       <c r="V434" s="1"/>
       <c r="W434" s="1"/>
     </row>
-    <row r="435" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="435" ht="12.75" customHeight="true">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -11540,7 +11916,7 @@
       <c r="V435" s="1"/>
       <c r="W435" s="1"/>
     </row>
-    <row r="436" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="436" ht="12.75" customHeight="true">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -11565,7 +11941,7 @@
       <c r="V436" s="1"/>
       <c r="W436" s="1"/>
     </row>
-    <row r="437" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="437" ht="12.75" customHeight="true">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -11590,7 +11966,7 @@
       <c r="V437" s="1"/>
       <c r="W437" s="1"/>
     </row>
-    <row r="438" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="438" ht="12.75" customHeight="true">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -11615,7 +11991,7 @@
       <c r="V438" s="1"/>
       <c r="W438" s="1"/>
     </row>
-    <row r="439" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="439" ht="12.75" customHeight="true">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -11640,7 +12016,7 @@
       <c r="V439" s="1"/>
       <c r="W439" s="1"/>
     </row>
-    <row r="440" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="440" ht="12.75" customHeight="true">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -11665,7 +12041,7 @@
       <c r="V440" s="1"/>
       <c r="W440" s="1"/>
     </row>
-    <row r="441" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="441" ht="12.75" customHeight="true">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -11690,7 +12066,7 @@
       <c r="V441" s="1"/>
       <c r="W441" s="1"/>
     </row>
-    <row r="442" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="442" ht="12.75" customHeight="true">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -11715,7 +12091,7 @@
       <c r="V442" s="1"/>
       <c r="W442" s="1"/>
     </row>
-    <row r="443" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="443" ht="12.75" customHeight="true">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -11740,7 +12116,7 @@
       <c r="V443" s="1"/>
       <c r="W443" s="1"/>
     </row>
-    <row r="444" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="444" ht="12.75" customHeight="true">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -11765,7 +12141,7 @@
       <c r="V444" s="1"/>
       <c r="W444" s="1"/>
     </row>
-    <row r="445" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="445" ht="12.75" customHeight="true">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -11790,7 +12166,7 @@
       <c r="V445" s="1"/>
       <c r="W445" s="1"/>
     </row>
-    <row r="446" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="446" ht="12.75" customHeight="true">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -11815,7 +12191,7 @@
       <c r="V446" s="1"/>
       <c r="W446" s="1"/>
     </row>
-    <row r="447" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="447" ht="12.75" customHeight="true">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -11840,7 +12216,7 @@
       <c r="V447" s="1"/>
       <c r="W447" s="1"/>
     </row>
-    <row r="448" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="448" ht="12.75" customHeight="true">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -11865,7 +12241,7 @@
       <c r="V448" s="1"/>
       <c r="W448" s="1"/>
     </row>
-    <row r="449" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="449" ht="12.75" customHeight="true">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -11890,7 +12266,7 @@
       <c r="V449" s="1"/>
       <c r="W449" s="1"/>
     </row>
-    <row r="450" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="450" ht="12.75" customHeight="true">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -11915,7 +12291,7 @@
       <c r="V450" s="1"/>
       <c r="W450" s="1"/>
     </row>
-    <row r="451" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="451" ht="12.75" customHeight="true">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -11940,7 +12316,7 @@
       <c r="V451" s="1"/>
       <c r="W451" s="1"/>
     </row>
-    <row r="452" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="452" ht="12.75" customHeight="true">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -11965,7 +12341,7 @@
       <c r="V452" s="1"/>
       <c r="W452" s="1"/>
     </row>
-    <row r="453" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="453" ht="12.75" customHeight="true">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -11990,7 +12366,7 @@
       <c r="V453" s="1"/>
       <c r="W453" s="1"/>
     </row>
-    <row r="454" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="454" ht="12.75" customHeight="true">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -12015,7 +12391,7 @@
       <c r="V454" s="1"/>
       <c r="W454" s="1"/>
     </row>
-    <row r="455" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="455" ht="12.75" customHeight="true">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -12040,7 +12416,7 @@
       <c r="V455" s="1"/>
       <c r="W455" s="1"/>
     </row>
-    <row r="456" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="456" ht="12.75" customHeight="true">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -12065,7 +12441,7 @@
       <c r="V456" s="1"/>
       <c r="W456" s="1"/>
     </row>
-    <row r="457" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="457" ht="12.75" customHeight="true">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -12090,7 +12466,7 @@
       <c r="V457" s="1"/>
       <c r="W457" s="1"/>
     </row>
-    <row r="458" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="458" ht="12.75" customHeight="true">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -12115,7 +12491,7 @@
       <c r="V458" s="1"/>
       <c r="W458" s="1"/>
     </row>
-    <row r="459" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="459" ht="12.75" customHeight="true">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -12140,7 +12516,7 @@
       <c r="V459" s="1"/>
       <c r="W459" s="1"/>
     </row>
-    <row r="460" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="460" ht="12.75" customHeight="true">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -12165,7 +12541,7 @@
       <c r="V460" s="1"/>
       <c r="W460" s="1"/>
     </row>
-    <row r="461" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="461" ht="12.75" customHeight="true">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -12190,7 +12566,7 @@
       <c r="V461" s="1"/>
       <c r="W461" s="1"/>
     </row>
-    <row r="462" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="462" ht="12.75" customHeight="true">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -12215,7 +12591,7 @@
       <c r="V462" s="1"/>
       <c r="W462" s="1"/>
     </row>
-    <row r="463" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="463" ht="12.75" customHeight="true">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -12240,7 +12616,7 @@
       <c r="V463" s="1"/>
       <c r="W463" s="1"/>
     </row>
-    <row r="464" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="464" ht="12.75" customHeight="true">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -12265,7 +12641,7 @@
       <c r="V464" s="1"/>
       <c r="W464" s="1"/>
     </row>
-    <row r="465" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="465" ht="12.75" customHeight="true">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -12290,7 +12666,7 @@
       <c r="V465" s="1"/>
       <c r="W465" s="1"/>
     </row>
-    <row r="466" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="466" ht="12.75" customHeight="true">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -12315,7 +12691,7 @@
       <c r="V466" s="1"/>
       <c r="W466" s="1"/>
     </row>
-    <row r="467" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="467" ht="12.75" customHeight="true">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -12340,7 +12716,7 @@
       <c r="V467" s="1"/>
       <c r="W467" s="1"/>
     </row>
-    <row r="468" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="468" ht="12.75" customHeight="true">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -12365,7 +12741,7 @@
       <c r="V468" s="1"/>
       <c r="W468" s="1"/>
     </row>
-    <row r="469" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="469" ht="12.75" customHeight="true">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -12390,7 +12766,7 @@
       <c r="V469" s="1"/>
       <c r="W469" s="1"/>
     </row>
-    <row r="470" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="470" ht="12.75" customHeight="true">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -12415,7 +12791,7 @@
       <c r="V470" s="1"/>
       <c r="W470" s="1"/>
     </row>
-    <row r="471" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="471" ht="12.75" customHeight="true">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -12440,7 +12816,7 @@
       <c r="V471" s="1"/>
       <c r="W471" s="1"/>
     </row>
-    <row r="472" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="472" ht="12.75" customHeight="true">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -12465,7 +12841,7 @@
       <c r="V472" s="1"/>
       <c r="W472" s="1"/>
     </row>
-    <row r="473" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="473" ht="12.75" customHeight="true">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -12490,7 +12866,7 @@
       <c r="V473" s="1"/>
       <c r="W473" s="1"/>
     </row>
-    <row r="474" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="474" ht="12.75" customHeight="true">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -12515,7 +12891,7 @@
       <c r="V474" s="1"/>
       <c r="W474" s="1"/>
     </row>
-    <row r="475" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="475" ht="12.75" customHeight="true">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -12540,7 +12916,7 @@
       <c r="V475" s="1"/>
       <c r="W475" s="1"/>
     </row>
-    <row r="476" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="476" ht="12.75" customHeight="true">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -12565,7 +12941,7 @@
       <c r="V476" s="1"/>
       <c r="W476" s="1"/>
     </row>
-    <row r="477" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="477" ht="12.75" customHeight="true">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -12590,7 +12966,7 @@
       <c r="V477" s="1"/>
       <c r="W477" s="1"/>
     </row>
-    <row r="478" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="478" ht="12.75" customHeight="true">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -12615,7 +12991,7 @@
       <c r="V478" s="1"/>
       <c r="W478" s="1"/>
     </row>
-    <row r="479" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="479" ht="12.75" customHeight="true">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -12640,7 +13016,7 @@
       <c r="V479" s="1"/>
       <c r="W479" s="1"/>
     </row>
-    <row r="480" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="480" ht="12.75" customHeight="true">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -12665,7 +13041,7 @@
       <c r="V480" s="1"/>
       <c r="W480" s="1"/>
     </row>
-    <row r="481" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="481" ht="12.75" customHeight="true">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -12690,7 +13066,7 @@
       <c r="V481" s="1"/>
       <c r="W481" s="1"/>
     </row>
-    <row r="482" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="482" ht="12.75" customHeight="true">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -12715,7 +13091,7 @@
       <c r="V482" s="1"/>
       <c r="W482" s="1"/>
     </row>
-    <row r="483" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="483" ht="12.75" customHeight="true">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -12740,7 +13116,7 @@
       <c r="V483" s="1"/>
       <c r="W483" s="1"/>
     </row>
-    <row r="484" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="484" ht="12.75" customHeight="true">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -12765,7 +13141,7 @@
       <c r="V484" s="1"/>
       <c r="W484" s="1"/>
     </row>
-    <row r="485" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="485" ht="12.75" customHeight="true">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -12790,7 +13166,7 @@
       <c r="V485" s="1"/>
       <c r="W485" s="1"/>
     </row>
-    <row r="486" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="486" ht="12.75" customHeight="true">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -12815,7 +13191,7 @@
       <c r="V486" s="1"/>
       <c r="W486" s="1"/>
     </row>
-    <row r="487" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="487" ht="12.75" customHeight="true">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -12840,7 +13216,7 @@
       <c r="V487" s="1"/>
       <c r="W487" s="1"/>
     </row>
-    <row r="488" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="488" ht="12.75" customHeight="true">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -12865,7 +13241,7 @@
       <c r="V488" s="1"/>
       <c r="W488" s="1"/>
     </row>
-    <row r="489" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="489" ht="12.75" customHeight="true">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -12890,7 +13266,7 @@
       <c r="V489" s="1"/>
       <c r="W489" s="1"/>
     </row>
-    <row r="490" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="490" ht="12.75" customHeight="true">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -12915,7 +13291,7 @@
       <c r="V490" s="1"/>
       <c r="W490" s="1"/>
     </row>
-    <row r="491" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="491" ht="12.75" customHeight="true">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -12940,7 +13316,7 @@
       <c r="V491" s="1"/>
       <c r="W491" s="1"/>
     </row>
-    <row r="492" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="492" ht="12.75" customHeight="true">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -12965,7 +13341,7 @@
       <c r="V492" s="1"/>
       <c r="W492" s="1"/>
     </row>
-    <row r="493" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="493" ht="12.75" customHeight="true">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -12990,7 +13366,7 @@
       <c r="V493" s="1"/>
       <c r="W493" s="1"/>
     </row>
-    <row r="494" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="494" ht="12.75" customHeight="true">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -13015,7 +13391,7 @@
       <c r="V494" s="1"/>
       <c r="W494" s="1"/>
     </row>
-    <row r="495" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="495" ht="12.75" customHeight="true">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -13040,7 +13416,7 @@
       <c r="V495" s="1"/>
       <c r="W495" s="1"/>
     </row>
-    <row r="496" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="496" ht="12.75" customHeight="true">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -13065,7 +13441,7 @@
       <c r="V496" s="1"/>
       <c r="W496" s="1"/>
     </row>
-    <row r="497" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="497" ht="12.75" customHeight="true">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -13090,7 +13466,7 @@
       <c r="V497" s="1"/>
       <c r="W497" s="1"/>
     </row>
-    <row r="498" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="498" ht="12.75" customHeight="true">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -13115,7 +13491,7 @@
       <c r="V498" s="1"/>
       <c r="W498" s="1"/>
     </row>
-    <row r="499" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="499" ht="12.75" customHeight="true">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -13140,7 +13516,7 @@
       <c r="V499" s="1"/>
       <c r="W499" s="1"/>
     </row>
-    <row r="500" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="500" ht="12.75" customHeight="true">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -13165,7 +13541,7 @@
       <c r="V500" s="1"/>
       <c r="W500" s="1"/>
     </row>
-    <row r="501" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="501" ht="12.75" customHeight="true">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -13190,7 +13566,7 @@
       <c r="V501" s="1"/>
       <c r="W501" s="1"/>
     </row>
-    <row r="502" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="502" ht="12.75" customHeight="true">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -13215,7 +13591,7 @@
       <c r="V502" s="1"/>
       <c r="W502" s="1"/>
     </row>
-    <row r="503" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="503" ht="12.75" customHeight="true">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -13240,7 +13616,7 @@
       <c r="V503" s="1"/>
       <c r="W503" s="1"/>
     </row>
-    <row r="504" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="504" ht="12.75" customHeight="true">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -13265,7 +13641,7 @@
       <c r="V504" s="1"/>
       <c r="W504" s="1"/>
     </row>
-    <row r="505" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="505" ht="12.75" customHeight="true">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -13290,7 +13666,7 @@
       <c r="V505" s="1"/>
       <c r="W505" s="1"/>
     </row>
-    <row r="506" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="506" ht="12.75" customHeight="true">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -13315,7 +13691,7 @@
       <c r="V506" s="1"/>
       <c r="W506" s="1"/>
     </row>
-    <row r="507" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="507" ht="12.75" customHeight="true">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -13340,7 +13716,7 @@
       <c r="V507" s="1"/>
       <c r="W507" s="1"/>
     </row>
-    <row r="508" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="508" ht="12.75" customHeight="true">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -13365,7 +13741,7 @@
       <c r="V508" s="1"/>
       <c r="W508" s="1"/>
     </row>
-    <row r="509" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="509" ht="12.75" customHeight="true">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -13390,7 +13766,7 @@
       <c r="V509" s="1"/>
       <c r="W509" s="1"/>
     </row>
-    <row r="510" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="510" ht="12.75" customHeight="true">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -13415,7 +13791,7 @@
       <c r="V510" s="1"/>
       <c r="W510" s="1"/>
     </row>
-    <row r="511" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="511" ht="12.75" customHeight="true">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -13440,7 +13816,7 @@
       <c r="V511" s="1"/>
       <c r="W511" s="1"/>
     </row>
-    <row r="512" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="512" ht="12.75" customHeight="true">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -13465,7 +13841,7 @@
       <c r="V512" s="1"/>
       <c r="W512" s="1"/>
     </row>
-    <row r="513" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="513" ht="12.75" customHeight="true">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -13490,7 +13866,7 @@
       <c r="V513" s="1"/>
       <c r="W513" s="1"/>
     </row>
-    <row r="514" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="514" ht="12.75" customHeight="true">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -13515,7 +13891,7 @@
       <c r="V514" s="1"/>
       <c r="W514" s="1"/>
     </row>
-    <row r="515" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="515" ht="12.75" customHeight="true">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -13540,7 +13916,7 @@
       <c r="V515" s="1"/>
       <c r="W515" s="1"/>
     </row>
-    <row r="516" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="516" ht="12.75" customHeight="true">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -13565,7 +13941,7 @@
       <c r="V516" s="1"/>
       <c r="W516" s="1"/>
     </row>
-    <row r="517" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="517" ht="12.75" customHeight="true">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -13590,7 +13966,7 @@
       <c r="V517" s="1"/>
       <c r="W517" s="1"/>
     </row>
-    <row r="518" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="518" ht="12.75" customHeight="true">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -13615,7 +13991,7 @@
       <c r="V518" s="1"/>
       <c r="W518" s="1"/>
     </row>
-    <row r="519" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="519" ht="12.75" customHeight="true">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -13640,7 +14016,7 @@
       <c r="V519" s="1"/>
       <c r="W519" s="1"/>
     </row>
-    <row r="520" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="520" ht="12.75" customHeight="true">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -13665,7 +14041,7 @@
       <c r="V520" s="1"/>
       <c r="W520" s="1"/>
     </row>
-    <row r="521" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="521" ht="12.75" customHeight="true">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -13690,7 +14066,7 @@
       <c r="V521" s="1"/>
       <c r="W521" s="1"/>
     </row>
-    <row r="522" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="522" ht="12.75" customHeight="true">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -13715,7 +14091,7 @@
       <c r="V522" s="1"/>
       <c r="W522" s="1"/>
     </row>
-    <row r="523" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="523" ht="12.75" customHeight="true">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -13740,7 +14116,7 @@
       <c r="V523" s="1"/>
       <c r="W523" s="1"/>
     </row>
-    <row r="524" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="524" ht="12.75" customHeight="true">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -13765,7 +14141,7 @@
       <c r="V524" s="1"/>
       <c r="W524" s="1"/>
     </row>
-    <row r="525" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="525" ht="12.75" customHeight="true">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -13790,7 +14166,7 @@
       <c r="V525" s="1"/>
       <c r="W525" s="1"/>
     </row>
-    <row r="526" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="526" ht="12.75" customHeight="true">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -13815,7 +14191,7 @@
       <c r="V526" s="1"/>
       <c r="W526" s="1"/>
     </row>
-    <row r="527" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="527" ht="12.75" customHeight="true">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -13840,7 +14216,7 @@
       <c r="V527" s="1"/>
       <c r="W527" s="1"/>
     </row>
-    <row r="528" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="528" ht="12.75" customHeight="true">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -13865,7 +14241,7 @@
       <c r="V528" s="1"/>
       <c r="W528" s="1"/>
     </row>
-    <row r="529" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="529" ht="12.75" customHeight="true">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -13890,7 +14266,7 @@
       <c r="V529" s="1"/>
       <c r="W529" s="1"/>
     </row>
-    <row r="530" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="530" ht="12.75" customHeight="true">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -13915,7 +14291,7 @@
       <c r="V530" s="1"/>
       <c r="W530" s="1"/>
     </row>
-    <row r="531" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="531" ht="12.75" customHeight="true">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -13940,7 +14316,7 @@
       <c r="V531" s="1"/>
       <c r="W531" s="1"/>
     </row>
-    <row r="532" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="532" ht="12.75" customHeight="true">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -13965,7 +14341,7 @@
       <c r="V532" s="1"/>
       <c r="W532" s="1"/>
     </row>
-    <row r="533" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="533" ht="12.75" customHeight="true">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -13990,7 +14366,7 @@
       <c r="V533" s="1"/>
       <c r="W533" s="1"/>
     </row>
-    <row r="534" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="534" ht="12.75" customHeight="true">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -14015,7 +14391,7 @@
       <c r="V534" s="1"/>
       <c r="W534" s="1"/>
     </row>
-    <row r="535" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="535" ht="12.75" customHeight="true">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -14040,7 +14416,7 @@
       <c r="V535" s="1"/>
       <c r="W535" s="1"/>
     </row>
-    <row r="536" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="536" ht="12.75" customHeight="true">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -14065,7 +14441,7 @@
       <c r="V536" s="1"/>
       <c r="W536" s="1"/>
     </row>
-    <row r="537" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="537" ht="12.75" customHeight="true">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -14090,7 +14466,7 @@
       <c r="V537" s="1"/>
       <c r="W537" s="1"/>
     </row>
-    <row r="538" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="538" ht="12.75" customHeight="true">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -14115,7 +14491,7 @@
       <c r="V538" s="1"/>
       <c r="W538" s="1"/>
     </row>
-    <row r="539" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="539" ht="12.75" customHeight="true">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -14140,7 +14516,7 @@
       <c r="V539" s="1"/>
       <c r="W539" s="1"/>
     </row>
-    <row r="540" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="540" ht="12.75" customHeight="true">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -14165,7 +14541,7 @@
       <c r="V540" s="1"/>
       <c r="W540" s="1"/>
     </row>
-    <row r="541" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="541" ht="12.75" customHeight="true">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -14190,7 +14566,7 @@
       <c r="V541" s="1"/>
       <c r="W541" s="1"/>
     </row>
-    <row r="542" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="542" ht="12.75" customHeight="true">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -14215,7 +14591,7 @@
       <c r="V542" s="1"/>
       <c r="W542" s="1"/>
     </row>
-    <row r="543" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="543" ht="12.75" customHeight="true">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -14240,7 +14616,7 @@
       <c r="V543" s="1"/>
       <c r="W543" s="1"/>
     </row>
-    <row r="544" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="544" ht="12.75" customHeight="true">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -14265,7 +14641,7 @@
       <c r="V544" s="1"/>
       <c r="W544" s="1"/>
     </row>
-    <row r="545" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="545" ht="12.75" customHeight="true">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -14290,7 +14666,7 @@
       <c r="V545" s="1"/>
       <c r="W545" s="1"/>
     </row>
-    <row r="546" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="546" ht="12.75" customHeight="true">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -14315,7 +14691,7 @@
       <c r="V546" s="1"/>
       <c r="W546" s="1"/>
     </row>
-    <row r="547" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="547" ht="12.75" customHeight="true">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -14340,7 +14716,7 @@
       <c r="V547" s="1"/>
       <c r="W547" s="1"/>
     </row>
-    <row r="548" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="548" ht="12.75" customHeight="true">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -14365,7 +14741,7 @@
       <c r="V548" s="1"/>
       <c r="W548" s="1"/>
     </row>
-    <row r="549" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="549" ht="12.75" customHeight="true">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -14390,7 +14766,7 @@
       <c r="V549" s="1"/>
       <c r="W549" s="1"/>
     </row>
-    <row r="550" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="550" ht="12.75" customHeight="true">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -14415,7 +14791,7 @@
       <c r="V550" s="1"/>
       <c r="W550" s="1"/>
     </row>
-    <row r="551" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="551" ht="12.75" customHeight="true">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -14440,7 +14816,7 @@
       <c r="V551" s="1"/>
       <c r="W551" s="1"/>
     </row>
-    <row r="552" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="552" ht="12.75" customHeight="true">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -14465,7 +14841,7 @@
       <c r="V552" s="1"/>
       <c r="W552" s="1"/>
     </row>
-    <row r="553" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="553" ht="12.75" customHeight="true">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -14490,7 +14866,7 @@
       <c r="V553" s="1"/>
       <c r="W553" s="1"/>
     </row>
-    <row r="554" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="554" ht="12.75" customHeight="true">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -14515,7 +14891,7 @@
       <c r="V554" s="1"/>
       <c r="W554" s="1"/>
     </row>
-    <row r="555" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="555" ht="12.75" customHeight="true">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -14540,7 +14916,7 @@
       <c r="V555" s="1"/>
       <c r="W555" s="1"/>
     </row>
-    <row r="556" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="556" ht="12.75" customHeight="true">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -14565,7 +14941,7 @@
       <c r="V556" s="1"/>
       <c r="W556" s="1"/>
     </row>
-    <row r="557" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="557" ht="12.75" customHeight="true">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -14590,7 +14966,7 @@
       <c r="V557" s="1"/>
       <c r="W557" s="1"/>
     </row>
-    <row r="558" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="558" ht="12.75" customHeight="true">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -14615,7 +14991,7 @@
       <c r="V558" s="1"/>
       <c r="W558" s="1"/>
     </row>
-    <row r="559" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="559" ht="12.75" customHeight="true">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -14640,7 +15016,7 @@
       <c r="V559" s="1"/>
       <c r="W559" s="1"/>
     </row>
-    <row r="560" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="560" ht="12.75" customHeight="true">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -14665,7 +15041,7 @@
       <c r="V560" s="1"/>
       <c r="W560" s="1"/>
     </row>
-    <row r="561" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="561" ht="12.75" customHeight="true">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -14690,7 +15066,7 @@
       <c r="V561" s="1"/>
       <c r="W561" s="1"/>
     </row>
-    <row r="562" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="562" ht="12.75" customHeight="true">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -14715,7 +15091,7 @@
       <c r="V562" s="1"/>
       <c r="W562" s="1"/>
     </row>
-    <row r="563" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="563" ht="12.75" customHeight="true">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -14740,7 +15116,7 @@
       <c r="V563" s="1"/>
       <c r="W563" s="1"/>
     </row>
-    <row r="564" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="564" ht="12.75" customHeight="true">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -14765,7 +15141,7 @@
       <c r="V564" s="1"/>
       <c r="W564" s="1"/>
     </row>
-    <row r="565" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="565" ht="12.75" customHeight="true">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -14790,7 +15166,7 @@
       <c r="V565" s="1"/>
       <c r="W565" s="1"/>
     </row>
-    <row r="566" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="566" ht="12.75" customHeight="true">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -14815,7 +15191,7 @@
       <c r="V566" s="1"/>
       <c r="W566" s="1"/>
     </row>
-    <row r="567" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="567" ht="12.75" customHeight="true">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -14840,7 +15216,7 @@
       <c r="V567" s="1"/>
       <c r="W567" s="1"/>
     </row>
-    <row r="568" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="568" ht="12.75" customHeight="true">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -14865,7 +15241,7 @@
       <c r="V568" s="1"/>
       <c r="W568" s="1"/>
     </row>
-    <row r="569" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="569" ht="12.75" customHeight="true">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -14890,7 +15266,7 @@
       <c r="V569" s="1"/>
       <c r="W569" s="1"/>
     </row>
-    <row r="570" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="570" ht="12.75" customHeight="true">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -14915,7 +15291,7 @@
       <c r="V570" s="1"/>
       <c r="W570" s="1"/>
     </row>
-    <row r="571" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="571" ht="12.75" customHeight="true">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -14940,7 +15316,7 @@
       <c r="V571" s="1"/>
       <c r="W571" s="1"/>
     </row>
-    <row r="572" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="572" ht="12.75" customHeight="true">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -14965,7 +15341,7 @@
       <c r="V572" s="1"/>
       <c r="W572" s="1"/>
     </row>
-    <row r="573" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="573" ht="12.75" customHeight="true">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -14990,7 +15366,7 @@
       <c r="V573" s="1"/>
       <c r="W573" s="1"/>
     </row>
-    <row r="574" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="574" ht="12.75" customHeight="true">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -15015,7 +15391,7 @@
       <c r="V574" s="1"/>
       <c r="W574" s="1"/>
     </row>
-    <row r="575" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="575" ht="12.75" customHeight="true">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -15040,7 +15416,7 @@
       <c r="V575" s="1"/>
       <c r="W575" s="1"/>
     </row>
-    <row r="576" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="576" ht="12.75" customHeight="true">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -15065,7 +15441,7 @@
       <c r="V576" s="1"/>
       <c r="W576" s="1"/>
     </row>
-    <row r="577" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="577" ht="12.75" customHeight="true">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -15090,7 +15466,7 @@
       <c r="V577" s="1"/>
       <c r="W577" s="1"/>
     </row>
-    <row r="578" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="578" ht="12.75" customHeight="true">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -15115,7 +15491,7 @@
       <c r="V578" s="1"/>
       <c r="W578" s="1"/>
     </row>
-    <row r="579" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="579" ht="12.75" customHeight="true">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -15140,7 +15516,7 @@
       <c r="V579" s="1"/>
       <c r="W579" s="1"/>
     </row>
-    <row r="580" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="580" ht="12.75" customHeight="true">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -15165,7 +15541,7 @@
       <c r="V580" s="1"/>
       <c r="W580" s="1"/>
     </row>
-    <row r="581" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="581" ht="12.75" customHeight="true">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -15190,7 +15566,7 @@
       <c r="V581" s="1"/>
       <c r="W581" s="1"/>
     </row>
-    <row r="582" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="582" ht="12.75" customHeight="true">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -15215,7 +15591,7 @@
       <c r="V582" s="1"/>
       <c r="W582" s="1"/>
     </row>
-    <row r="583" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="583" ht="12.75" customHeight="true">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -15240,7 +15616,7 @@
       <c r="V583" s="1"/>
       <c r="W583" s="1"/>
     </row>
-    <row r="584" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="584" ht="12.75" customHeight="true">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -15265,7 +15641,7 @@
       <c r="V584" s="1"/>
       <c r="W584" s="1"/>
     </row>
-    <row r="585" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="585" ht="12.75" customHeight="true">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -15290,7 +15666,7 @@
       <c r="V585" s="1"/>
       <c r="W585" s="1"/>
     </row>
-    <row r="586" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="586" ht="12.75" customHeight="true">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -15315,7 +15691,7 @@
       <c r="V586" s="1"/>
       <c r="W586" s="1"/>
     </row>
-    <row r="587" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="587" ht="12.75" customHeight="true">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -15340,7 +15716,7 @@
       <c r="V587" s="1"/>
       <c r="W587" s="1"/>
     </row>
-    <row r="588" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="588" ht="12.75" customHeight="true">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -15365,7 +15741,7 @@
       <c r="V588" s="1"/>
       <c r="W588" s="1"/>
     </row>
-    <row r="589" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="589" ht="12.75" customHeight="true">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -15390,7 +15766,7 @@
       <c r="V589" s="1"/>
       <c r="W589" s="1"/>
     </row>
-    <row r="590" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="590" ht="12.75" customHeight="true">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -15415,7 +15791,7 @@
       <c r="V590" s="1"/>
       <c r="W590" s="1"/>
     </row>
-    <row r="591" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="591" ht="12.75" customHeight="true">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -15440,7 +15816,7 @@
       <c r="V591" s="1"/>
       <c r="W591" s="1"/>
     </row>
-    <row r="592" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="592" ht="12.75" customHeight="true">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -15465,7 +15841,7 @@
       <c r="V592" s="1"/>
       <c r="W592" s="1"/>
     </row>
-    <row r="593" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="593" ht="12.75" customHeight="true">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -15490,7 +15866,7 @@
       <c r="V593" s="1"/>
       <c r="W593" s="1"/>
     </row>
-    <row r="594" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="594" ht="12.75" customHeight="true">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -15515,7 +15891,7 @@
       <c r="V594" s="1"/>
       <c r="W594" s="1"/>
     </row>
-    <row r="595" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="595" ht="12.75" customHeight="true">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -15540,7 +15916,7 @@
       <c r="V595" s="1"/>
       <c r="W595" s="1"/>
     </row>
-    <row r="596" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="596" ht="12.75" customHeight="true">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -15565,7 +15941,7 @@
       <c r="V596" s="1"/>
       <c r="W596" s="1"/>
     </row>
-    <row r="597" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="597" ht="12.75" customHeight="true">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -15590,7 +15966,7 @@
       <c r="V597" s="1"/>
       <c r="W597" s="1"/>
     </row>
-    <row r="598" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="598" ht="12.75" customHeight="true">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -15615,7 +15991,7 @@
       <c r="V598" s="1"/>
       <c r="W598" s="1"/>
     </row>
-    <row r="599" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="599" ht="12.75" customHeight="true">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -15640,7 +16016,7 @@
       <c r="V599" s="1"/>
       <c r="W599" s="1"/>
     </row>
-    <row r="600" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="600" ht="12.75" customHeight="true">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -15665,7 +16041,7 @@
       <c r="V600" s="1"/>
       <c r="W600" s="1"/>
     </row>
-    <row r="601" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="601" ht="12.75" customHeight="true">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -15690,7 +16066,7 @@
       <c r="V601" s="1"/>
       <c r="W601" s="1"/>
     </row>
-    <row r="602" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="602" ht="12.75" customHeight="true">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -15715,7 +16091,7 @@
       <c r="V602" s="1"/>
       <c r="W602" s="1"/>
     </row>
-    <row r="603" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="603" ht="12.75" customHeight="true">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -15740,7 +16116,7 @@
       <c r="V603" s="1"/>
       <c r="W603" s="1"/>
     </row>
-    <row r="604" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="604" ht="12.75" customHeight="true">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -15765,7 +16141,7 @@
       <c r="V604" s="1"/>
       <c r="W604" s="1"/>
     </row>
-    <row r="605" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="605" ht="12.75" customHeight="true">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -15790,7 +16166,7 @@
       <c r="V605" s="1"/>
       <c r="W605" s="1"/>
     </row>
-    <row r="606" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="606" ht="12.75" customHeight="true">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -15815,7 +16191,7 @@
       <c r="V606" s="1"/>
       <c r="W606" s="1"/>
     </row>
-    <row r="607" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="607" ht="12.75" customHeight="true">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -15840,7 +16216,7 @@
       <c r="V607" s="1"/>
       <c r="W607" s="1"/>
     </row>
-    <row r="608" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="608" ht="12.75" customHeight="true">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -15865,7 +16241,7 @@
       <c r="V608" s="1"/>
       <c r="W608" s="1"/>
     </row>
-    <row r="609" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="609" ht="12.75" customHeight="true">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -15890,7 +16266,7 @@
       <c r="V609" s="1"/>
       <c r="W609" s="1"/>
     </row>
-    <row r="610" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="610" ht="12.75" customHeight="true">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -15915,7 +16291,7 @@
       <c r="V610" s="1"/>
       <c r="W610" s="1"/>
     </row>
-    <row r="611" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="611" ht="12.75" customHeight="true">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -15940,7 +16316,7 @@
       <c r="V611" s="1"/>
       <c r="W611" s="1"/>
     </row>
-    <row r="612" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="612" ht="12.75" customHeight="true">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -15965,7 +16341,7 @@
       <c r="V612" s="1"/>
       <c r="W612" s="1"/>
     </row>
-    <row r="613" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="613" ht="12.75" customHeight="true">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -15990,7 +16366,7 @@
       <c r="V613" s="1"/>
       <c r="W613" s="1"/>
     </row>
-    <row r="614" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="614" ht="12.75" customHeight="true">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -16015,7 +16391,7 @@
       <c r="V614" s="1"/>
       <c r="W614" s="1"/>
     </row>
-    <row r="615" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="615" ht="12.75" customHeight="true">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -16040,7 +16416,7 @@
       <c r="V615" s="1"/>
       <c r="W615" s="1"/>
     </row>
-    <row r="616" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="616" ht="12.75" customHeight="true">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -16065,7 +16441,7 @@
       <c r="V616" s="1"/>
       <c r="W616" s="1"/>
     </row>
-    <row r="617" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="617" ht="12.75" customHeight="true">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -16090,7 +16466,7 @@
       <c r="V617" s="1"/>
       <c r="W617" s="1"/>
     </row>
-    <row r="618" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="618" ht="12.75" customHeight="true">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -16115,7 +16491,7 @@
       <c r="V618" s="1"/>
       <c r="W618" s="1"/>
     </row>
-    <row r="619" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="619" ht="12.75" customHeight="true">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -16140,7 +16516,7 @@
       <c r="V619" s="1"/>
       <c r="W619" s="1"/>
     </row>
-    <row r="620" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="620" ht="12.75" customHeight="true">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -16165,7 +16541,7 @@
       <c r="V620" s="1"/>
       <c r="W620" s="1"/>
     </row>
-    <row r="621" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="621" ht="12.75" customHeight="true">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -16190,7 +16566,7 @@
       <c r="V621" s="1"/>
       <c r="W621" s="1"/>
     </row>
-    <row r="622" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="622" ht="12.75" customHeight="true">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -16215,7 +16591,7 @@
       <c r="V622" s="1"/>
       <c r="W622" s="1"/>
     </row>
-    <row r="623" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="623" ht="12.75" customHeight="true">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -16240,7 +16616,7 @@
       <c r="V623" s="1"/>
       <c r="W623" s="1"/>
     </row>
-    <row r="624" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="624" ht="12.75" customHeight="true">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -16265,7 +16641,7 @@
       <c r="V624" s="1"/>
       <c r="W624" s="1"/>
     </row>
-    <row r="625" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="625" ht="12.75" customHeight="true">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -16290,7 +16666,7 @@
       <c r="V625" s="1"/>
       <c r="W625" s="1"/>
     </row>
-    <row r="626" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="626" ht="12.75" customHeight="true">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -16315,7 +16691,7 @@
       <c r="V626" s="1"/>
       <c r="W626" s="1"/>
     </row>
-    <row r="627" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="627" ht="12.75" customHeight="true">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -16340,7 +16716,7 @@
       <c r="V627" s="1"/>
       <c r="W627" s="1"/>
     </row>
-    <row r="628" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="628" ht="12.75" customHeight="true">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -16365,7 +16741,7 @@
       <c r="V628" s="1"/>
       <c r="W628" s="1"/>
     </row>
-    <row r="629" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="629" ht="12.75" customHeight="true">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -16390,7 +16766,7 @@
       <c r="V629" s="1"/>
       <c r="W629" s="1"/>
     </row>
-    <row r="630" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="630" ht="12.75" customHeight="true">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -16415,7 +16791,7 @@
       <c r="V630" s="1"/>
       <c r="W630" s="1"/>
     </row>
-    <row r="631" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="631" ht="12.75" customHeight="true">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -16440,7 +16816,7 @@
       <c r="V631" s="1"/>
       <c r="W631" s="1"/>
     </row>
-    <row r="632" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="632" ht="12.75" customHeight="true">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -16465,7 +16841,7 @@
       <c r="V632" s="1"/>
       <c r="W632" s="1"/>
     </row>
-    <row r="633" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="633" ht="12.75" customHeight="true">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -16490,7 +16866,7 @@
       <c r="V633" s="1"/>
       <c r="W633" s="1"/>
     </row>
-    <row r="634" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="634" ht="12.75" customHeight="true">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -16515,7 +16891,7 @@
       <c r="V634" s="1"/>
       <c r="W634" s="1"/>
     </row>
-    <row r="635" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="635" ht="12.75" customHeight="true">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -16540,7 +16916,7 @@
       <c r="V635" s="1"/>
       <c r="W635" s="1"/>
     </row>
-    <row r="636" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="636" ht="12.75" customHeight="true">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -16565,7 +16941,7 @@
       <c r="V636" s="1"/>
       <c r="W636" s="1"/>
     </row>
-    <row r="637" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="637" ht="12.75" customHeight="true">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -16590,7 +16966,7 @@
       <c r="V637" s="1"/>
       <c r="W637" s="1"/>
     </row>
-    <row r="638" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="638" ht="12.75" customHeight="true">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -16615,7 +16991,7 @@
       <c r="V638" s="1"/>
       <c r="W638" s="1"/>
     </row>
-    <row r="639" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="639" ht="12.75" customHeight="true">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -16640,7 +17016,7 @@
       <c r="V639" s="1"/>
       <c r="W639" s="1"/>
     </row>
-    <row r="640" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="640" ht="12.75" customHeight="true">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -16665,7 +17041,7 @@
       <c r="V640" s="1"/>
       <c r="W640" s="1"/>
     </row>
-    <row r="641" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="641" ht="12.75" customHeight="true">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -16690,7 +17066,7 @@
       <c r="V641" s="1"/>
       <c r="W641" s="1"/>
     </row>
-    <row r="642" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="642" ht="12.75" customHeight="true">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -16715,7 +17091,7 @@
       <c r="V642" s="1"/>
       <c r="W642" s="1"/>
     </row>
-    <row r="643" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="643" ht="12.75" customHeight="true">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -16740,7 +17116,7 @@
       <c r="V643" s="1"/>
       <c r="W643" s="1"/>
     </row>
-    <row r="644" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="644" ht="12.75" customHeight="true">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -16765,7 +17141,7 @@
       <c r="V644" s="1"/>
       <c r="W644" s="1"/>
     </row>
-    <row r="645" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="645" ht="12.75" customHeight="true">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -16790,7 +17166,7 @@
       <c r="V645" s="1"/>
       <c r="W645" s="1"/>
     </row>
-    <row r="646" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="646" ht="12.75" customHeight="true">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -16815,7 +17191,7 @@
       <c r="V646" s="1"/>
       <c r="W646" s="1"/>
     </row>
-    <row r="647" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="647" ht="12.75" customHeight="true">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -16840,7 +17216,7 @@
       <c r="V647" s="1"/>
       <c r="W647" s="1"/>
     </row>
-    <row r="648" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="648" ht="12.75" customHeight="true">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -16865,7 +17241,7 @@
       <c r="V648" s="1"/>
       <c r="W648" s="1"/>
     </row>
-    <row r="649" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="649" ht="12.75" customHeight="true">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -16890,7 +17266,7 @@
       <c r="V649" s="1"/>
       <c r="W649" s="1"/>
     </row>
-    <row r="650" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="650" ht="12.75" customHeight="true">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -16915,7 +17291,7 @@
       <c r="V650" s="1"/>
       <c r="W650" s="1"/>
     </row>
-    <row r="651" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="651" ht="12.75" customHeight="true">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -16940,7 +17316,7 @@
       <c r="V651" s="1"/>
       <c r="W651" s="1"/>
     </row>
-    <row r="652" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="652" ht="12.75" customHeight="true">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -16965,7 +17341,7 @@
       <c r="V652" s="1"/>
       <c r="W652" s="1"/>
     </row>
-    <row r="653" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="653" ht="12.75" customHeight="true">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -16990,7 +17366,7 @@
       <c r="V653" s="1"/>
       <c r="W653" s="1"/>
     </row>
-    <row r="654" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="654" ht="12.75" customHeight="true">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -17015,7 +17391,7 @@
       <c r="V654" s="1"/>
       <c r="W654" s="1"/>
     </row>
-    <row r="655" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="655" ht="12.75" customHeight="true">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -17040,7 +17416,7 @@
       <c r="V655" s="1"/>
       <c r="W655" s="1"/>
     </row>
-    <row r="656" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="656" ht="12.75" customHeight="true">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -17065,7 +17441,7 @@
       <c r="V656" s="1"/>
       <c r="W656" s="1"/>
     </row>
-    <row r="657" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="657" ht="12.75" customHeight="true">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -17090,7 +17466,7 @@
       <c r="V657" s="1"/>
       <c r="W657" s="1"/>
     </row>
-    <row r="658" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="658" ht="12.75" customHeight="true">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -17115,7 +17491,7 @@
       <c r="V658" s="1"/>
       <c r="W658" s="1"/>
     </row>
-    <row r="659" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="659" ht="12.75" customHeight="true">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -17140,7 +17516,7 @@
       <c r="V659" s="1"/>
       <c r="W659" s="1"/>
     </row>
-    <row r="660" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="660" ht="12.75" customHeight="true">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -17165,7 +17541,7 @@
       <c r="V660" s="1"/>
       <c r="W660" s="1"/>
     </row>
-    <row r="661" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="661" ht="12.75" customHeight="true">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -17190,7 +17566,7 @@
       <c r="V661" s="1"/>
       <c r="W661" s="1"/>
     </row>
-    <row r="662" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="662" ht="12.75" customHeight="true">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -17215,7 +17591,7 @@
       <c r="V662" s="1"/>
       <c r="W662" s="1"/>
     </row>
-    <row r="663" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="663" ht="12.75" customHeight="true">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -17240,7 +17616,7 @@
       <c r="V663" s="1"/>
       <c r="W663" s="1"/>
     </row>
-    <row r="664" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="664" ht="12.75" customHeight="true">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -17265,7 +17641,7 @@
       <c r="V664" s="1"/>
       <c r="W664" s="1"/>
     </row>
-    <row r="665" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="665" ht="12.75" customHeight="true">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -17290,7 +17666,7 @@
       <c r="V665" s="1"/>
       <c r="W665" s="1"/>
     </row>
-    <row r="666" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="666" ht="12.75" customHeight="true">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -17315,7 +17691,7 @@
       <c r="V666" s="1"/>
       <c r="W666" s="1"/>
     </row>
-    <row r="667" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="667" ht="12.75" customHeight="true">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -17340,7 +17716,7 @@
       <c r="V667" s="1"/>
       <c r="W667" s="1"/>
     </row>
-    <row r="668" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="668" ht="12.75" customHeight="true">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -17365,7 +17741,7 @@
       <c r="V668" s="1"/>
       <c r="W668" s="1"/>
     </row>
-    <row r="669" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="669" ht="12.75" customHeight="true">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -17390,7 +17766,7 @@
       <c r="V669" s="1"/>
       <c r="W669" s="1"/>
     </row>
-    <row r="670" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="670" ht="12.75" customHeight="true">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -17415,7 +17791,7 @@
       <c r="V670" s="1"/>
       <c r="W670" s="1"/>
     </row>
-    <row r="671" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="671" ht="12.75" customHeight="true">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -17440,7 +17816,7 @@
       <c r="V671" s="1"/>
       <c r="W671" s="1"/>
     </row>
-    <row r="672" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="672" ht="12.75" customHeight="true">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -17465,7 +17841,7 @@
       <c r="V672" s="1"/>
       <c r="W672" s="1"/>
     </row>
-    <row r="673" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="673" ht="12.75" customHeight="true">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -17490,7 +17866,7 @@
       <c r="V673" s="1"/>
       <c r="W673" s="1"/>
     </row>
-    <row r="674" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="674" ht="12.75" customHeight="true">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -17515,7 +17891,7 @@
       <c r="V674" s="1"/>
       <c r="W674" s="1"/>
     </row>
-    <row r="675" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="675" ht="12.75" customHeight="true">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -17540,7 +17916,7 @@
       <c r="V675" s="1"/>
       <c r="W675" s="1"/>
     </row>
-    <row r="676" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="676" ht="12.75" customHeight="true">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -17565,7 +17941,7 @@
       <c r="V676" s="1"/>
       <c r="W676" s="1"/>
     </row>
-    <row r="677" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="677" ht="12.75" customHeight="true">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -17590,7 +17966,7 @@
       <c r="V677" s="1"/>
       <c r="W677" s="1"/>
     </row>
-    <row r="678" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="678" ht="12.75" customHeight="true">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -17615,7 +17991,7 @@
       <c r="V678" s="1"/>
       <c r="W678" s="1"/>
     </row>
-    <row r="679" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="679" ht="12.75" customHeight="true">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -17640,7 +18016,7 @@
       <c r="V679" s="1"/>
       <c r="W679" s="1"/>
     </row>
-    <row r="680" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="680" ht="12.75" customHeight="true">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -17665,7 +18041,7 @@
       <c r="V680" s="1"/>
       <c r="W680" s="1"/>
     </row>
-    <row r="681" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="681" ht="12.75" customHeight="true">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -17690,7 +18066,7 @@
       <c r="V681" s="1"/>
       <c r="W681" s="1"/>
     </row>
-    <row r="682" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="682" ht="12.75" customHeight="true">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -17715,7 +18091,7 @@
       <c r="V682" s="1"/>
       <c r="W682" s="1"/>
     </row>
-    <row r="683" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="683" ht="12.75" customHeight="true">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -17740,7 +18116,7 @@
       <c r="V683" s="1"/>
       <c r="W683" s="1"/>
     </row>
-    <row r="684" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="684" ht="12.75" customHeight="true">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -17765,7 +18141,7 @@
       <c r="V684" s="1"/>
       <c r="W684" s="1"/>
     </row>
-    <row r="685" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="685" ht="12.75" customHeight="true">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -17790,7 +18166,7 @@
       <c r="V685" s="1"/>
       <c r="W685" s="1"/>
     </row>
-    <row r="686" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="686" ht="12.75" customHeight="true">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -17815,7 +18191,7 @@
       <c r="V686" s="1"/>
       <c r="W686" s="1"/>
     </row>
-    <row r="687" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="687" ht="12.75" customHeight="true">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -17840,7 +18216,7 @@
       <c r="V687" s="1"/>
       <c r="W687" s="1"/>
     </row>
-    <row r="688" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="688" ht="12.75" customHeight="true">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -17865,7 +18241,7 @@
       <c r="V688" s="1"/>
       <c r="W688" s="1"/>
     </row>
-    <row r="689" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="689" ht="12.75" customHeight="true">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -17890,7 +18266,7 @@
       <c r="V689" s="1"/>
       <c r="W689" s="1"/>
     </row>
-    <row r="690" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="690" ht="12.75" customHeight="true">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -17915,7 +18291,7 @@
       <c r="V690" s="1"/>
       <c r="W690" s="1"/>
     </row>
-    <row r="691" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="691" ht="12.75" customHeight="true">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -17940,7 +18316,7 @@
       <c r="V691" s="1"/>
       <c r="W691" s="1"/>
     </row>
-    <row r="692" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="692" ht="12.75" customHeight="true">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -17965,7 +18341,7 @@
       <c r="V692" s="1"/>
       <c r="W692" s="1"/>
     </row>
-    <row r="693" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="693" ht="12.75" customHeight="true">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -17990,7 +18366,7 @@
       <c r="V693" s="1"/>
       <c r="W693" s="1"/>
     </row>
-    <row r="694" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="694" ht="12.75" customHeight="true">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -18015,7 +18391,7 @@
       <c r="V694" s="1"/>
       <c r="W694" s="1"/>
     </row>
-    <row r="695" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="695" ht="12.75" customHeight="true">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -18040,7 +18416,7 @@
       <c r="V695" s="1"/>
       <c r="W695" s="1"/>
     </row>
-    <row r="696" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="696" ht="12.75" customHeight="true">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -18065,7 +18441,7 @@
       <c r="V696" s="1"/>
       <c r="W696" s="1"/>
     </row>
-    <row r="697" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="697" ht="12.75" customHeight="true">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -18090,7 +18466,7 @@
       <c r="V697" s="1"/>
       <c r="W697" s="1"/>
     </row>
-    <row r="698" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="698" ht="12.75" customHeight="true">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -18115,7 +18491,7 @@
       <c r="V698" s="1"/>
       <c r="W698" s="1"/>
     </row>
-    <row r="699" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="699" ht="12.75" customHeight="true">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -18140,7 +18516,7 @@
       <c r="V699" s="1"/>
       <c r="W699" s="1"/>
     </row>
-    <row r="700" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="700" ht="12.75" customHeight="true">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -18165,7 +18541,7 @@
       <c r="V700" s="1"/>
       <c r="W700" s="1"/>
     </row>
-    <row r="701" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="701" ht="12.75" customHeight="true">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -18190,7 +18566,7 @@
       <c r="V701" s="1"/>
       <c r="W701" s="1"/>
     </row>
-    <row r="702" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="702" ht="12.75" customHeight="true">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -18215,7 +18591,7 @@
       <c r="V702" s="1"/>
       <c r="W702" s="1"/>
     </row>
-    <row r="703" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="703" ht="12.75" customHeight="true">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -18240,7 +18616,7 @@
       <c r="V703" s="1"/>
       <c r="W703" s="1"/>
     </row>
-    <row r="704" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="704" ht="12.75" customHeight="true">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -18265,7 +18641,7 @@
       <c r="V704" s="1"/>
       <c r="W704" s="1"/>
     </row>
-    <row r="705" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="705" ht="12.75" customHeight="true">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -18290,7 +18666,7 @@
       <c r="V705" s="1"/>
       <c r="W705" s="1"/>
     </row>
-    <row r="706" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="706" ht="12.75" customHeight="true">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -18315,7 +18691,7 @@
       <c r="V706" s="1"/>
       <c r="W706" s="1"/>
     </row>
-    <row r="707" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="707" ht="12.75" customHeight="true">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -18340,7 +18716,7 @@
       <c r="V707" s="1"/>
       <c r="W707" s="1"/>
     </row>
-    <row r="708" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="708" ht="12.75" customHeight="true">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -18365,7 +18741,7 @@
       <c r="V708" s="1"/>
       <c r="W708" s="1"/>
     </row>
-    <row r="709" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="709" ht="12.75" customHeight="true">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -18390,7 +18766,7 @@
       <c r="V709" s="1"/>
       <c r="W709" s="1"/>
     </row>
-    <row r="710" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="710" ht="12.75" customHeight="true">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -18415,7 +18791,7 @@
       <c r="V710" s="1"/>
       <c r="W710" s="1"/>
     </row>
-    <row r="711" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="711" ht="12.75" customHeight="true">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -18440,7 +18816,7 @@
       <c r="V711" s="1"/>
       <c r="W711" s="1"/>
     </row>
-    <row r="712" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="712" ht="12.75" customHeight="true">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -18465,7 +18841,7 @@
       <c r="V712" s="1"/>
       <c r="W712" s="1"/>
     </row>
-    <row r="713" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="713" ht="12.75" customHeight="true">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -18490,7 +18866,7 @@
       <c r="V713" s="1"/>
       <c r="W713" s="1"/>
     </row>
-    <row r="714" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="714" ht="12.75" customHeight="true">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -18515,7 +18891,7 @@
       <c r="V714" s="1"/>
       <c r="W714" s="1"/>
     </row>
-    <row r="715" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="715" ht="12.75" customHeight="true">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -18540,7 +18916,7 @@
       <c r="V715" s="1"/>
       <c r="W715" s="1"/>
     </row>
-    <row r="716" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="716" ht="12.75" customHeight="true">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -18565,7 +18941,7 @@
       <c r="V716" s="1"/>
       <c r="W716" s="1"/>
     </row>
-    <row r="717" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="717" ht="12.75" customHeight="true">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -18590,7 +18966,7 @@
       <c r="V717" s="1"/>
       <c r="W717" s="1"/>
     </row>
-    <row r="718" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="718" ht="12.75" customHeight="true">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -18615,7 +18991,7 @@
       <c r="V718" s="1"/>
       <c r="W718" s="1"/>
     </row>
-    <row r="719" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="719" ht="12.75" customHeight="true">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -18640,7 +19016,7 @@
       <c r="V719" s="1"/>
       <c r="W719" s="1"/>
     </row>
-    <row r="720" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="720" ht="12.75" customHeight="true">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -18665,7 +19041,7 @@
       <c r="V720" s="1"/>
       <c r="W720" s="1"/>
     </row>
-    <row r="721" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="721" ht="12.75" customHeight="true">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -18690,7 +19066,7 @@
       <c r="V721" s="1"/>
       <c r="W721" s="1"/>
     </row>
-    <row r="722" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="722" ht="12.75" customHeight="true">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -18715,7 +19091,7 @@
       <c r="V722" s="1"/>
       <c r="W722" s="1"/>
     </row>
-    <row r="723" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="723" ht="12.75" customHeight="true">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -18740,7 +19116,7 @@
       <c r="V723" s="1"/>
       <c r="W723" s="1"/>
     </row>
-    <row r="724" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="724" ht="12.75" customHeight="true">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -18765,7 +19141,7 @@
       <c r="V724" s="1"/>
       <c r="W724" s="1"/>
     </row>
-    <row r="725" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="725" ht="12.75" customHeight="true">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -18790,7 +19166,7 @@
       <c r="V725" s="1"/>
       <c r="W725" s="1"/>
     </row>
-    <row r="726" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="726" ht="12.75" customHeight="true">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -18815,7 +19191,7 @@
       <c r="V726" s="1"/>
       <c r="W726" s="1"/>
     </row>
-    <row r="727" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="727" ht="12.75" customHeight="true">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -18840,7 +19216,7 @@
       <c r="V727" s="1"/>
       <c r="W727" s="1"/>
     </row>
-    <row r="728" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="728" ht="12.75" customHeight="true">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -18865,7 +19241,7 @@
       <c r="V728" s="1"/>
       <c r="W728" s="1"/>
     </row>
-    <row r="729" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="729" ht="12.75" customHeight="true">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -18890,7 +19266,7 @@
       <c r="V729" s="1"/>
       <c r="W729" s="1"/>
     </row>
-    <row r="730" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="730" ht="12.75" customHeight="true">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -18915,7 +19291,7 @@
       <c r="V730" s="1"/>
       <c r="W730" s="1"/>
     </row>
-    <row r="731" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="731" ht="12.75" customHeight="true">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -18940,7 +19316,7 @@
       <c r="V731" s="1"/>
       <c r="W731" s="1"/>
     </row>
-    <row r="732" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="732" ht="12.75" customHeight="true">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -18965,7 +19341,7 @@
       <c r="V732" s="1"/>
       <c r="W732" s="1"/>
     </row>
-    <row r="733" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="733" ht="12.75" customHeight="true">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -18990,7 +19366,7 @@
       <c r="V733" s="1"/>
       <c r="W733" s="1"/>
     </row>
-    <row r="734" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="734" ht="12.75" customHeight="true">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -19015,7 +19391,7 @@
       <c r="V734" s="1"/>
       <c r="W734" s="1"/>
     </row>
-    <row r="735" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="735" ht="12.75" customHeight="true">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -19040,7 +19416,7 @@
       <c r="V735" s="1"/>
       <c r="W735" s="1"/>
     </row>
-    <row r="736" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="736" ht="12.75" customHeight="true">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -19065,7 +19441,7 @@
       <c r="V736" s="1"/>
       <c r="W736" s="1"/>
     </row>
-    <row r="737" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="737" ht="12.75" customHeight="true">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -19090,7 +19466,7 @@
       <c r="V737" s="1"/>
       <c r="W737" s="1"/>
     </row>
-    <row r="738" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="738" ht="12.75" customHeight="true">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -19115,7 +19491,7 @@
       <c r="V738" s="1"/>
       <c r="W738" s="1"/>
     </row>
-    <row r="739" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="739" ht="12.75" customHeight="true">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -19140,7 +19516,7 @@
       <c r="V739" s="1"/>
       <c r="W739" s="1"/>
     </row>
-    <row r="740" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="740" ht="12.75" customHeight="true">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -19165,7 +19541,7 @@
       <c r="V740" s="1"/>
       <c r="W740" s="1"/>
     </row>
-    <row r="741" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="741" ht="12.75" customHeight="true">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -19190,7 +19566,7 @@
       <c r="V741" s="1"/>
       <c r="W741" s="1"/>
     </row>
-    <row r="742" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="742" ht="12.75" customHeight="true">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -19215,7 +19591,7 @@
       <c r="V742" s="1"/>
       <c r="W742" s="1"/>
     </row>
-    <row r="743" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="743" ht="12.75" customHeight="true">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -19240,7 +19616,7 @@
       <c r="V743" s="1"/>
       <c r="W743" s="1"/>
     </row>
-    <row r="744" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="744" ht="12.75" customHeight="true">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -19265,7 +19641,7 @@
       <c r="V744" s="1"/>
       <c r="W744" s="1"/>
     </row>
-    <row r="745" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="745" ht="12.75" customHeight="true">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -19290,7 +19666,7 @@
       <c r="V745" s="1"/>
       <c r="W745" s="1"/>
     </row>
-    <row r="746" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="746" ht="12.75" customHeight="true">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -19315,7 +19691,7 @@
       <c r="V746" s="1"/>
       <c r="W746" s="1"/>
     </row>
-    <row r="747" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="747" ht="12.75" customHeight="true">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -19340,7 +19716,7 @@
       <c r="V747" s="1"/>
       <c r="W747" s="1"/>
     </row>
-    <row r="748" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="748" ht="12.75" customHeight="true">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -19365,7 +19741,7 @@
       <c r="V748" s="1"/>
       <c r="W748" s="1"/>
     </row>
-    <row r="749" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="749" ht="12.75" customHeight="true">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -19390,7 +19766,7 @@
       <c r="V749" s="1"/>
       <c r="W749" s="1"/>
     </row>
-    <row r="750" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="750" ht="12.75" customHeight="true">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -19415,7 +19791,7 @@
       <c r="V750" s="1"/>
       <c r="W750" s="1"/>
     </row>
-    <row r="751" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="751" ht="12.75" customHeight="true">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -19440,7 +19816,7 @@
       <c r="V751" s="1"/>
       <c r="W751" s="1"/>
     </row>
-    <row r="752" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="752" ht="12.75" customHeight="true">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -19465,7 +19841,7 @@
       <c r="V752" s="1"/>
       <c r="W752" s="1"/>
     </row>
-    <row r="753" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="753" ht="12.75" customHeight="true">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -19490,7 +19866,7 @@
       <c r="V753" s="1"/>
       <c r="W753" s="1"/>
     </row>
-    <row r="754" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="754" ht="12.75" customHeight="true">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -19515,7 +19891,7 @@
       <c r="V754" s="1"/>
       <c r="W754" s="1"/>
     </row>
-    <row r="755" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="755" ht="12.75" customHeight="true">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -19540,7 +19916,7 @@
       <c r="V755" s="1"/>
       <c r="W755" s="1"/>
     </row>
-    <row r="756" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="756" ht="12.75" customHeight="true">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -19565,7 +19941,7 @@
       <c r="V756" s="1"/>
       <c r="W756" s="1"/>
     </row>
-    <row r="757" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="757" ht="12.75" customHeight="true">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -19590,7 +19966,7 @@
       <c r="V757" s="1"/>
       <c r="W757" s="1"/>
     </row>
-    <row r="758" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="758" ht="12.75" customHeight="true">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -19615,7 +19991,7 @@
       <c r="V758" s="1"/>
       <c r="W758" s="1"/>
     </row>
-    <row r="759" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="759" ht="12.75" customHeight="true">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -19640,7 +20016,7 @@
       <c r="V759" s="1"/>
       <c r="W759" s="1"/>
     </row>
-    <row r="760" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="760" ht="12.75" customHeight="true">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -19665,7 +20041,7 @@
       <c r="V760" s="1"/>
       <c r="W760" s="1"/>
     </row>
-    <row r="761" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="761" ht="12.75" customHeight="true">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -19690,7 +20066,7 @@
       <c r="V761" s="1"/>
       <c r="W761" s="1"/>
     </row>
-    <row r="762" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="762" ht="12.75" customHeight="true">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -19715,7 +20091,7 @@
       <c r="V762" s="1"/>
       <c r="W762" s="1"/>
     </row>
-    <row r="763" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="763" ht="12.75" customHeight="true">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -19740,7 +20116,7 @@
       <c r="V763" s="1"/>
       <c r="W763" s="1"/>
     </row>
-    <row r="764" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="764" ht="12.75" customHeight="true">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -19765,7 +20141,7 @@
       <c r="V764" s="1"/>
       <c r="W764" s="1"/>
     </row>
-    <row r="765" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="765" ht="12.75" customHeight="true">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -19790,7 +20166,7 @@
       <c r="V765" s="1"/>
       <c r="W765" s="1"/>
     </row>
-    <row r="766" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="766" ht="12.75" customHeight="true">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -19815,7 +20191,7 @@
       <c r="V766" s="1"/>
       <c r="W766" s="1"/>
     </row>
-    <row r="767" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="767" ht="12.75" customHeight="true">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -19840,7 +20216,7 @@
       <c r="V767" s="1"/>
       <c r="W767" s="1"/>
     </row>
-    <row r="768" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="768" ht="12.75" customHeight="true">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -19865,7 +20241,7 @@
       <c r="V768" s="1"/>
       <c r="W768" s="1"/>
     </row>
-    <row r="769" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="769" ht="12.75" customHeight="true">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -19890,7 +20266,7 @@
       <c r="V769" s="1"/>
       <c r="W769" s="1"/>
     </row>
-    <row r="770" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="770" ht="12.75" customHeight="true">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -19915,7 +20291,7 @@
       <c r="V770" s="1"/>
       <c r="W770" s="1"/>
     </row>
-    <row r="771" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="771" ht="12.75" customHeight="true">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -19940,7 +20316,7 @@
       <c r="V771" s="1"/>
       <c r="W771" s="1"/>
     </row>
-    <row r="772" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="772" ht="12.75" customHeight="true">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -19965,7 +20341,7 @@
       <c r="V772" s="1"/>
       <c r="W772" s="1"/>
     </row>
-    <row r="773" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="773" ht="12.75" customHeight="true">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -19990,7 +20366,7 @@
       <c r="V773" s="1"/>
       <c r="W773" s="1"/>
     </row>
-    <row r="774" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="774" ht="12.75" customHeight="true">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -20015,7 +20391,7 @@
       <c r="V774" s="1"/>
       <c r="W774" s="1"/>
     </row>
-    <row r="775" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="775" ht="12.75" customHeight="true">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -20040,7 +20416,7 @@
       <c r="V775" s="1"/>
       <c r="W775" s="1"/>
     </row>
-    <row r="776" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="776" ht="12.75" customHeight="true">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -20065,7 +20441,7 @@
       <c r="V776" s="1"/>
       <c r="W776" s="1"/>
     </row>
-    <row r="777" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="777" ht="12.75" customHeight="true">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -20090,7 +20466,7 @@
       <c r="V777" s="1"/>
       <c r="W777" s="1"/>
     </row>
-    <row r="778" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="778" ht="12.75" customHeight="true">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -20115,7 +20491,7 @@
       <c r="V778" s="1"/>
       <c r="W778" s="1"/>
     </row>
-    <row r="779" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="779" ht="12.75" customHeight="true">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -20140,7 +20516,7 @@
       <c r="V779" s="1"/>
       <c r="W779" s="1"/>
     </row>
-    <row r="780" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="780" ht="12.75" customHeight="true">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -20165,7 +20541,7 @@
       <c r="V780" s="1"/>
       <c r="W780" s="1"/>
     </row>
-    <row r="781" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="781" ht="12.75" customHeight="true">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -20190,7 +20566,7 @@
       <c r="V781" s="1"/>
       <c r="W781" s="1"/>
     </row>
-    <row r="782" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="782" ht="12.75" customHeight="true">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -20215,7 +20591,7 @@
       <c r="V782" s="1"/>
       <c r="W782" s="1"/>
     </row>
-    <row r="783" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="783" ht="12.75" customHeight="true">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -20240,7 +20616,7 @@
       <c r="V783" s="1"/>
       <c r="W783" s="1"/>
     </row>
-    <row r="784" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="784" ht="12.75" customHeight="true">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -20265,7 +20641,7 @@
       <c r="V784" s="1"/>
       <c r="W784" s="1"/>
     </row>
-    <row r="785" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="785" ht="12.75" customHeight="true">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -20290,7 +20666,7 @@
       <c r="V785" s="1"/>
       <c r="W785" s="1"/>
     </row>
-    <row r="786" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="786" ht="12.75" customHeight="true">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -20315,7 +20691,7 @@
       <c r="V786" s="1"/>
       <c r="W786" s="1"/>
     </row>
-    <row r="787" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="787" ht="12.75" customHeight="true">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -20340,7 +20716,7 @@
       <c r="V787" s="1"/>
       <c r="W787" s="1"/>
     </row>
-    <row r="788" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="788" ht="12.75" customHeight="true">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -20365,7 +20741,7 @@
       <c r="V788" s="1"/>
       <c r="W788" s="1"/>
     </row>
-    <row r="789" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="789" ht="12.75" customHeight="true">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -20390,7 +20766,7 @@
       <c r="V789" s="1"/>
       <c r="W789" s="1"/>
     </row>
-    <row r="790" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="790" ht="12.75" customHeight="true">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -20415,7 +20791,7 @@
       <c r="V790" s="1"/>
       <c r="W790" s="1"/>
     </row>
-    <row r="791" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="791" ht="12.75" customHeight="true">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -20440,7 +20816,7 @@
       <c r="V791" s="1"/>
       <c r="W791" s="1"/>
     </row>
-    <row r="792" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="792" ht="12.75" customHeight="true">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -20465,7 +20841,7 @@
       <c r="V792" s="1"/>
       <c r="W792" s="1"/>
     </row>
-    <row r="793" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="793" ht="12.75" customHeight="true">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -20490,7 +20866,7 @@
       <c r="V793" s="1"/>
       <c r="W793" s="1"/>
     </row>
-    <row r="794" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="794" ht="12.75" customHeight="true">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -20515,7 +20891,7 @@
       <c r="V794" s="1"/>
       <c r="W794" s="1"/>
     </row>
-    <row r="795" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="795" ht="12.75" customHeight="true">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -20540,7 +20916,7 @@
       <c r="V795" s="1"/>
       <c r="W795" s="1"/>
     </row>
-    <row r="796" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="796" ht="12.75" customHeight="true">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -20565,7 +20941,7 @@
       <c r="V796" s="1"/>
       <c r="W796" s="1"/>
     </row>
-    <row r="797" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="797" ht="12.75" customHeight="true">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -20590,7 +20966,7 @@
       <c r="V797" s="1"/>
       <c r="W797" s="1"/>
     </row>
-    <row r="798" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="798" ht="12.75" customHeight="true">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -20615,7 +20991,7 @@
       <c r="V798" s="1"/>
       <c r="W798" s="1"/>
     </row>
-    <row r="799" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="799" ht="12.75" customHeight="true">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -20640,7 +21016,7 @@
       <c r="V799" s="1"/>
       <c r="W799" s="1"/>
     </row>
-    <row r="800" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="800" ht="12.75" customHeight="true">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -20665,7 +21041,7 @@
       <c r="V800" s="1"/>
       <c r="W800" s="1"/>
     </row>
-    <row r="801" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="801" ht="12.75" customHeight="true">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -20690,7 +21066,7 @@
       <c r="V801" s="1"/>
       <c r="W801" s="1"/>
     </row>
-    <row r="802" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="802" ht="12.75" customHeight="true">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -20715,7 +21091,7 @@
       <c r="V802" s="1"/>
       <c r="W802" s="1"/>
     </row>
-    <row r="803" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="803" ht="12.75" customHeight="true">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -20740,7 +21116,7 @@
       <c r="V803" s="1"/>
       <c r="W803" s="1"/>
     </row>
-    <row r="804" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="804" ht="12.75" customHeight="true">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -20765,7 +21141,7 @@
       <c r="V804" s="1"/>
       <c r="W804" s="1"/>
     </row>
-    <row r="805" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="805" ht="12.75" customHeight="true">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -20790,7 +21166,7 @@
       <c r="V805" s="1"/>
       <c r="W805" s="1"/>
     </row>
-    <row r="806" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="806" ht="12.75" customHeight="true">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -20815,7 +21191,7 @@
       <c r="V806" s="1"/>
       <c r="W806" s="1"/>
     </row>
-    <row r="807" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="807" ht="12.75" customHeight="true">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -20840,7 +21216,7 @@
       <c r="V807" s="1"/>
       <c r="W807" s="1"/>
     </row>
-    <row r="808" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="808" ht="12.75" customHeight="true">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -20865,7 +21241,7 @@
       <c r="V808" s="1"/>
       <c r="W808" s="1"/>
     </row>
-    <row r="809" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="809" ht="12.75" customHeight="true">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -20890,7 +21266,7 @@
       <c r="V809" s="1"/>
       <c r="W809" s="1"/>
     </row>
-    <row r="810" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="810" ht="12.75" customHeight="true">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -20915,7 +21291,7 @@
       <c r="V810" s="1"/>
       <c r="W810" s="1"/>
     </row>
-    <row r="811" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="811" ht="12.75" customHeight="true">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -20940,7 +21316,7 @@
       <c r="V811" s="1"/>
       <c r="W811" s="1"/>
     </row>
-    <row r="812" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="812" ht="12.75" customHeight="true">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -20965,7 +21341,7 @@
       <c r="V812" s="1"/>
       <c r="W812" s="1"/>
     </row>
-    <row r="813" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="813" ht="12.75" customHeight="true">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -20990,7 +21366,7 @@
       <c r="V813" s="1"/>
       <c r="W813" s="1"/>
     </row>
-    <row r="814" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="814" ht="12.75" customHeight="true">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -21015,7 +21391,7 @@
       <c r="V814" s="1"/>
       <c r="W814" s="1"/>
     </row>
-    <row r="815" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="815" ht="12.75" customHeight="true">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -21040,7 +21416,7 @@
       <c r="V815" s="1"/>
       <c r="W815" s="1"/>
     </row>
-    <row r="816" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="816" ht="12.75" customHeight="true">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -21065,7 +21441,7 @@
       <c r="V816" s="1"/>
       <c r="W816" s="1"/>
     </row>
-    <row r="817" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="817" ht="12.75" customHeight="true">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -21090,7 +21466,7 @@
       <c r="V817" s="1"/>
       <c r="W817" s="1"/>
     </row>
-    <row r="818" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="818" ht="12.75" customHeight="true">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -21115,7 +21491,7 @@
       <c r="V818" s="1"/>
       <c r="W818" s="1"/>
     </row>
-    <row r="819" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="819" ht="12.75" customHeight="true">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -21140,7 +21516,7 @@
       <c r="V819" s="1"/>
       <c r="W819" s="1"/>
     </row>
-    <row r="820" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="820" ht="12.75" customHeight="true">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -21165,7 +21541,7 @@
       <c r="V820" s="1"/>
       <c r="W820" s="1"/>
     </row>
-    <row r="821" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="821" ht="12.75" customHeight="true">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -21190,7 +21566,7 @@
       <c r="V821" s="1"/>
       <c r="W821" s="1"/>
     </row>
-    <row r="822" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="822" ht="12.75" customHeight="true">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -21215,7 +21591,7 @@
       <c r="V822" s="1"/>
       <c r="W822" s="1"/>
     </row>
-    <row r="823" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="823" ht="12.75" customHeight="true">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -21240,7 +21616,7 @@
       <c r="V823" s="1"/>
       <c r="W823" s="1"/>
     </row>
-    <row r="824" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="824" ht="12.75" customHeight="true">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -21265,7 +21641,7 @@
       <c r="V824" s="1"/>
       <c r="W824" s="1"/>
     </row>
-    <row r="825" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="825" ht="12.75" customHeight="true">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -21290,7 +21666,7 @@
       <c r="V825" s="1"/>
       <c r="W825" s="1"/>
     </row>
-    <row r="826" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="826" ht="12.75" customHeight="true">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -21315,7 +21691,7 @@
       <c r="V826" s="1"/>
       <c r="W826" s="1"/>
     </row>
-    <row r="827" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="827" ht="12.75" customHeight="true">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -21340,7 +21716,7 @@
       <c r="V827" s="1"/>
       <c r="W827" s="1"/>
     </row>
-    <row r="828" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="828" ht="12.75" customHeight="true">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -21365,7 +21741,7 @@
       <c r="V828" s="1"/>
       <c r="W828" s="1"/>
     </row>
-    <row r="829" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="829" ht="12.75" customHeight="true">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -21390,7 +21766,7 @@
       <c r="V829" s="1"/>
       <c r="W829" s="1"/>
     </row>
-    <row r="830" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="830" ht="12.75" customHeight="true">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -21415,7 +21791,7 @@
       <c r="V830" s="1"/>
       <c r="W830" s="1"/>
     </row>
-    <row r="831" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="831" ht="12.75" customHeight="true">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -21440,7 +21816,7 @@
       <c r="V831" s="1"/>
       <c r="W831" s="1"/>
     </row>
-    <row r="832" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="832" ht="12.75" customHeight="true">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -21465,7 +21841,7 @@
       <c r="V832" s="1"/>
       <c r="W832" s="1"/>
     </row>
-    <row r="833" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="833" ht="12.75" customHeight="true">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -21490,7 +21866,7 @@
       <c r="V833" s="1"/>
       <c r="W833" s="1"/>
     </row>
-    <row r="834" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="834" ht="12.75" customHeight="true">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -21515,7 +21891,7 @@
       <c r="V834" s="1"/>
       <c r="W834" s="1"/>
     </row>
-    <row r="835" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="835" ht="12.75" customHeight="true">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -21540,7 +21916,7 @@
       <c r="V835" s="1"/>
       <c r="W835" s="1"/>
     </row>
-    <row r="836" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="836" ht="12.75" customHeight="true">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -21565,7 +21941,7 @@
       <c r="V836" s="1"/>
       <c r="W836" s="1"/>
     </row>
-    <row r="837" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="837" ht="12.75" customHeight="true">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -21590,7 +21966,7 @@
       <c r="V837" s="1"/>
       <c r="W837" s="1"/>
     </row>
-    <row r="838" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="838" ht="12.75" customHeight="true">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -21615,7 +21991,7 @@
       <c r="V838" s="1"/>
       <c r="W838" s="1"/>
     </row>
-    <row r="839" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="839" ht="12.75" customHeight="true">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -21640,7 +22016,7 @@
       <c r="V839" s="1"/>
       <c r="W839" s="1"/>
     </row>
-    <row r="840" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="840" ht="12.75" customHeight="true">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -21665,7 +22041,7 @@
       <c r="V840" s="1"/>
       <c r="W840" s="1"/>
     </row>
-    <row r="841" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="841" ht="12.75" customHeight="true">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -21690,7 +22066,7 @@
       <c r="V841" s="1"/>
       <c r="W841" s="1"/>
     </row>
-    <row r="842" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="842" ht="12.75" customHeight="true">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -21715,7 +22091,7 @@
       <c r="V842" s="1"/>
       <c r="W842" s="1"/>
     </row>
-    <row r="843" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="843" ht="12.75" customHeight="true">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -21740,7 +22116,7 @@
       <c r="V843" s="1"/>
       <c r="W843" s="1"/>
     </row>
-    <row r="844" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="844" ht="12.75" customHeight="true">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -21765,7 +22141,7 @@
       <c r="V844" s="1"/>
       <c r="W844" s="1"/>
     </row>
-    <row r="845" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="845" ht="12.75" customHeight="true">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -21790,7 +22166,7 @@
       <c r="V845" s="1"/>
       <c r="W845" s="1"/>
     </row>
-    <row r="846" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="846" ht="12.75" customHeight="true">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -21815,7 +22191,7 @@
       <c r="V846" s="1"/>
       <c r="W846" s="1"/>
     </row>
-    <row r="847" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="847" ht="12.75" customHeight="true">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -21840,7 +22216,7 @@
       <c r="V847" s="1"/>
       <c r="W847" s="1"/>
     </row>
-    <row r="848" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="848" ht="12.75" customHeight="true">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -21865,7 +22241,7 @@
       <c r="V848" s="1"/>
       <c r="W848" s="1"/>
     </row>
-    <row r="849" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="849" ht="12.75" customHeight="true">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -21890,7 +22266,7 @@
       <c r="V849" s="1"/>
       <c r="W849" s="1"/>
     </row>
-    <row r="850" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="850" ht="12.75" customHeight="true">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -21915,7 +22291,7 @@
       <c r="V850" s="1"/>
       <c r="W850" s="1"/>
     </row>
-    <row r="851" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="851" ht="12.75" customHeight="true">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -21940,7 +22316,7 @@
       <c r="V851" s="1"/>
       <c r="W851" s="1"/>
     </row>
-    <row r="852" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="852" ht="12.75" customHeight="true">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -21965,7 +22341,7 @@
       <c r="V852" s="1"/>
       <c r="W852" s="1"/>
     </row>
-    <row r="853" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="853" ht="12.75" customHeight="true">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -21990,7 +22366,7 @@
       <c r="V853" s="1"/>
       <c r="W853" s="1"/>
     </row>
-    <row r="854" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="854" ht="12.75" customHeight="true">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -22015,7 +22391,7 @@
       <c r="V854" s="1"/>
       <c r="W854" s="1"/>
     </row>
-    <row r="855" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="855" ht="12.75" customHeight="true">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -22040,7 +22416,7 @@
       <c r="V855" s="1"/>
       <c r="W855" s="1"/>
     </row>
-    <row r="856" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="856" ht="12.75" customHeight="true">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -22065,7 +22441,7 @@
       <c r="V856" s="1"/>
       <c r="W856" s="1"/>
     </row>
-    <row r="857" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="857" ht="12.75" customHeight="true">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -22090,7 +22466,7 @@
       <c r="V857" s="1"/>
       <c r="W857" s="1"/>
     </row>
-    <row r="858" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="858" ht="12.75" customHeight="true">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -22115,7 +22491,7 @@
       <c r="V858" s="1"/>
       <c r="W858" s="1"/>
     </row>
-    <row r="859" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="859" ht="12.75" customHeight="true">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -22140,7 +22516,7 @@
       <c r="V859" s="1"/>
       <c r="W859" s="1"/>
     </row>
-    <row r="860" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="860" ht="12.75" customHeight="true">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -22165,7 +22541,7 @@
       <c r="V860" s="1"/>
       <c r="W860" s="1"/>
     </row>
-    <row r="861" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="861" ht="12.75" customHeight="true">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -22190,7 +22566,7 @@
       <c r="V861" s="1"/>
       <c r="W861" s="1"/>
     </row>
-    <row r="862" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="862" ht="12.75" customHeight="true">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -22215,7 +22591,7 @@
       <c r="V862" s="1"/>
       <c r="W862" s="1"/>
     </row>
-    <row r="863" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="863" ht="12.75" customHeight="true">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -22240,7 +22616,7 @@
       <c r="V863" s="1"/>
       <c r="W863" s="1"/>
     </row>
-    <row r="864" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="864" ht="12.75" customHeight="true">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -22265,7 +22641,7 @@
       <c r="V864" s="1"/>
       <c r="W864" s="1"/>
     </row>
-    <row r="865" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="865" ht="12.75" customHeight="true">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -22290,7 +22666,7 @@
       <c r="V865" s="1"/>
       <c r="W865" s="1"/>
     </row>
-    <row r="866" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="866" ht="12.75" customHeight="true">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -22315,7 +22691,7 @@
       <c r="V866" s="1"/>
       <c r="W866" s="1"/>
     </row>
-    <row r="867" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="867" ht="12.75" customHeight="true">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -22340,7 +22716,7 @@
       <c r="V867" s="1"/>
       <c r="W867" s="1"/>
     </row>
-    <row r="868" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="868" ht="12.75" customHeight="true">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -22365,7 +22741,7 @@
       <c r="V868" s="1"/>
       <c r="W868" s="1"/>
     </row>
-    <row r="869" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="869" ht="12.75" customHeight="true">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -22390,7 +22766,7 @@
       <c r="V869" s="1"/>
       <c r="W869" s="1"/>
     </row>
-    <row r="870" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="870" ht="12.75" customHeight="true">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -22415,7 +22791,7 @@
       <c r="V870" s="1"/>
       <c r="W870" s="1"/>
     </row>
-    <row r="871" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="871" ht="12.75" customHeight="true">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -22440,7 +22816,7 @@
       <c r="V871" s="1"/>
       <c r="W871" s="1"/>
     </row>
-    <row r="872" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="872" ht="12.75" customHeight="true">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -22465,7 +22841,7 @@
       <c r="V872" s="1"/>
       <c r="W872" s="1"/>
     </row>
-    <row r="873" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="873" ht="12.75" customHeight="true">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -22490,7 +22866,7 @@
       <c r="V873" s="1"/>
       <c r="W873" s="1"/>
     </row>
-    <row r="874" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="874" ht="12.75" customHeight="true">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -22515,7 +22891,7 @@
       <c r="V874" s="1"/>
       <c r="W874" s="1"/>
     </row>
-    <row r="875" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="875" ht="12.75" customHeight="true">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -22540,7 +22916,7 @@
       <c r="V875" s="1"/>
       <c r="W875" s="1"/>
     </row>
-    <row r="876" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="876" ht="12.75" customHeight="true">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -22565,7 +22941,7 @@
       <c r="V876" s="1"/>
       <c r="W876" s="1"/>
     </row>
-    <row r="877" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="877" ht="12.75" customHeight="true">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -22590,7 +22966,7 @@
       <c r="V877" s="1"/>
       <c r="W877" s="1"/>
     </row>
-    <row r="878" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="878" ht="12.75" customHeight="true">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -22615,7 +22991,7 @@
       <c r="V878" s="1"/>
       <c r="W878" s="1"/>
     </row>
-    <row r="879" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="879" ht="12.75" customHeight="true">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -22640,7 +23016,7 @@
       <c r="V879" s="1"/>
       <c r="W879" s="1"/>
     </row>
-    <row r="880" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="880" ht="12.75" customHeight="true">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -22665,7 +23041,7 @@
       <c r="V880" s="1"/>
       <c r="W880" s="1"/>
     </row>
-    <row r="881" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="881" ht="12.75" customHeight="true">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -22690,7 +23066,7 @@
       <c r="V881" s="1"/>
       <c r="W881" s="1"/>
     </row>
-    <row r="882" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="882" ht="12.75" customHeight="true">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -22715,7 +23091,7 @@
       <c r="V882" s="1"/>
       <c r="W882" s="1"/>
     </row>
-    <row r="883" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="883" ht="12.75" customHeight="true">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -22740,7 +23116,7 @@
       <c r="V883" s="1"/>
       <c r="W883" s="1"/>
     </row>
-    <row r="884" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="884" ht="12.75" customHeight="true">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -22765,7 +23141,7 @@
       <c r="V884" s="1"/>
       <c r="W884" s="1"/>
     </row>
-    <row r="885" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="885" ht="12.75" customHeight="true">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -22790,7 +23166,7 @@
       <c r="V885" s="1"/>
       <c r="W885" s="1"/>
     </row>
-    <row r="886" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="886" ht="12.75" customHeight="true">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -22815,7 +23191,7 @@
       <c r="V886" s="1"/>
       <c r="W886" s="1"/>
     </row>
-    <row r="887" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="887" ht="12.75" customHeight="true">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -22840,7 +23216,7 @@
       <c r="V887" s="1"/>
       <c r="W887" s="1"/>
     </row>
-    <row r="888" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="888" ht="12.75" customHeight="true">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -22865,7 +23241,7 @@
       <c r="V888" s="1"/>
       <c r="W888" s="1"/>
     </row>
-    <row r="889" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="889" ht="12.75" customHeight="true">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -22890,7 +23266,7 @@
       <c r="V889" s="1"/>
       <c r="W889" s="1"/>
     </row>
-    <row r="890" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="890" ht="12.75" customHeight="true">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -22915,7 +23291,7 @@
       <c r="V890" s="1"/>
       <c r="W890" s="1"/>
     </row>
-    <row r="891" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="891" ht="12.75" customHeight="true">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -22940,7 +23316,7 @@
       <c r="V891" s="1"/>
       <c r="W891" s="1"/>
     </row>
-    <row r="892" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="892" ht="12.75" customHeight="true">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -22965,7 +23341,7 @@
       <c r="V892" s="1"/>
       <c r="W892" s="1"/>
     </row>
-    <row r="893" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="893" ht="12.75" customHeight="true">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -22990,7 +23366,7 @@
       <c r="V893" s="1"/>
       <c r="W893" s="1"/>
     </row>
-    <row r="894" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="894" ht="12.75" customHeight="true">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -23015,7 +23391,7 @@
       <c r="V894" s="1"/>
       <c r="W894" s="1"/>
     </row>
-    <row r="895" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="895" ht="12.75" customHeight="true">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -23040,7 +23416,7 @@
       <c r="V895" s="1"/>
       <c r="W895" s="1"/>
     </row>
-    <row r="896" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="896" ht="12.75" customHeight="true">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -23065,7 +23441,7 @@
       <c r="V896" s="1"/>
       <c r="W896" s="1"/>
     </row>
-    <row r="897" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="897" ht="12.75" customHeight="true">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -23090,7 +23466,7 @@
       <c r="V897" s="1"/>
       <c r="W897" s="1"/>
     </row>
-    <row r="898" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="898" ht="12.75" customHeight="true">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -23115,7 +23491,7 @@
       <c r="V898" s="1"/>
       <c r="W898" s="1"/>
     </row>
-    <row r="899" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="899" ht="12.75" customHeight="true">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -23140,7 +23516,7 @@
       <c r="V899" s="1"/>
       <c r="W899" s="1"/>
     </row>
-    <row r="900" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="900" ht="12.75" customHeight="true">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -23165,7 +23541,7 @@
       <c r="V900" s="1"/>
       <c r="W900" s="1"/>
     </row>
-    <row r="901" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="901" ht="12.75" customHeight="true">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -23190,7 +23566,7 @@
       <c r="V901" s="1"/>
       <c r="W901" s="1"/>
     </row>
-    <row r="902" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="902" ht="12.75" customHeight="true">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -23215,7 +23591,7 @@
       <c r="V902" s="1"/>
       <c r="W902" s="1"/>
     </row>
-    <row r="903" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="903" ht="12.75" customHeight="true">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -23240,7 +23616,7 @@
       <c r="V903" s="1"/>
       <c r="W903" s="1"/>
     </row>
-    <row r="904" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="904" ht="12.75" customHeight="true">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -23265,7 +23641,7 @@
       <c r="V904" s="1"/>
       <c r="W904" s="1"/>
     </row>
-    <row r="905" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="905" ht="12.75" customHeight="true">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -23290,7 +23666,7 @@
       <c r="V905" s="1"/>
       <c r="W905" s="1"/>
     </row>
-    <row r="906" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="906" ht="12.75" customHeight="true">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -23315,7 +23691,7 @@
       <c r="V906" s="1"/>
       <c r="W906" s="1"/>
     </row>
-    <row r="907" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="907" ht="12.75" customHeight="true">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -23340,7 +23716,7 @@
       <c r="V907" s="1"/>
       <c r="W907" s="1"/>
     </row>
-    <row r="908" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="908" ht="12.75" customHeight="true">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -23365,7 +23741,7 @@
       <c r="V908" s="1"/>
       <c r="W908" s="1"/>
     </row>
-    <row r="909" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="909" ht="12.75" customHeight="true">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -23390,7 +23766,7 @@
       <c r="V909" s="1"/>
       <c r="W909" s="1"/>
     </row>
-    <row r="910" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="910" ht="12.75" customHeight="true">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -23415,7 +23791,7 @@
       <c r="V910" s="1"/>
       <c r="W910" s="1"/>
     </row>
-    <row r="911" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="911" ht="12.75" customHeight="true">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -23440,7 +23816,7 @@
       <c r="V911" s="1"/>
       <c r="W911" s="1"/>
     </row>
-    <row r="912" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="912" ht="12.75" customHeight="true">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -23465,7 +23841,7 @@
       <c r="V912" s="1"/>
       <c r="W912" s="1"/>
     </row>
-    <row r="913" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="913" ht="12.75" customHeight="true">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -23490,7 +23866,7 @@
       <c r="V913" s="1"/>
       <c r="W913" s="1"/>
     </row>
-    <row r="914" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="914" ht="12.75" customHeight="true">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -23515,7 +23891,7 @@
       <c r="V914" s="1"/>
       <c r="W914" s="1"/>
     </row>
-    <row r="915" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="915" ht="12.75" customHeight="true">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -23540,7 +23916,7 @@
       <c r="V915" s="1"/>
       <c r="W915" s="1"/>
     </row>
-    <row r="916" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="916" ht="12.75" customHeight="true">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -23565,7 +23941,7 @@
       <c r="V916" s="1"/>
       <c r="W916" s="1"/>
     </row>
-    <row r="917" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="917" ht="12.75" customHeight="true">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -23590,7 +23966,7 @@
       <c r="V917" s="1"/>
       <c r="W917" s="1"/>
     </row>
-    <row r="918" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="918" ht="12.75" customHeight="true">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -23615,7 +23991,7 @@
       <c r="V918" s="1"/>
       <c r="W918" s="1"/>
     </row>
-    <row r="919" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="919" ht="12.75" customHeight="true">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -23640,7 +24016,7 @@
       <c r="V919" s="1"/>
       <c r="W919" s="1"/>
     </row>
-    <row r="920" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="920" ht="12.75" customHeight="true">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -23665,7 +24041,7 @@
       <c r="V920" s="1"/>
       <c r="W920" s="1"/>
     </row>
-    <row r="921" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="921" ht="12.75" customHeight="true">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -23690,7 +24066,7 @@
       <c r="V921" s="1"/>
       <c r="W921" s="1"/>
     </row>
-    <row r="922" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="922" ht="12.75" customHeight="true">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -23715,7 +24091,7 @@
       <c r="V922" s="1"/>
       <c r="W922" s="1"/>
     </row>
-    <row r="923" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="923" ht="12.75" customHeight="true">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -23740,7 +24116,7 @@
       <c r="V923" s="1"/>
       <c r="W923" s="1"/>
     </row>
-    <row r="924" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="924" ht="12.75" customHeight="true">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -23765,7 +24141,7 @@
       <c r="V924" s="1"/>
       <c r="W924" s="1"/>
     </row>
-    <row r="925" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="925" ht="12.75" customHeight="true">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -23790,7 +24166,7 @@
       <c r="V925" s="1"/>
       <c r="W925" s="1"/>
     </row>
-    <row r="926" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="926" ht="12.75" customHeight="true">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -23815,7 +24191,7 @@
       <c r="V926" s="1"/>
       <c r="W926" s="1"/>
     </row>
-    <row r="927" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="927" ht="12.75" customHeight="true">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -23840,7 +24216,7 @@
       <c r="V927" s="1"/>
       <c r="W927" s="1"/>
     </row>
-    <row r="928" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="928" ht="12.75" customHeight="true">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -23865,7 +24241,7 @@
       <c r="V928" s="1"/>
       <c r="W928" s="1"/>
     </row>
-    <row r="929" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="929" ht="12.75" customHeight="true">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -23890,7 +24266,7 @@
       <c r="V929" s="1"/>
       <c r="W929" s="1"/>
     </row>
-    <row r="930" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="930" ht="12.75" customHeight="true">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -23915,7 +24291,7 @@
       <c r="V930" s="1"/>
       <c r="W930" s="1"/>
     </row>
-    <row r="931" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="931" ht="12.75" customHeight="true">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -23940,7 +24316,7 @@
       <c r="V931" s="1"/>
       <c r="W931" s="1"/>
     </row>
-    <row r="932" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="932" ht="12.75" customHeight="true">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -23965,7 +24341,7 @@
       <c r="V932" s="1"/>
       <c r="W932" s="1"/>
     </row>
-    <row r="933" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="933" ht="12.75" customHeight="true">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -23990,7 +24366,7 @@
       <c r="V933" s="1"/>
       <c r="W933" s="1"/>
     </row>
-    <row r="934" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="934" ht="12.75" customHeight="true">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -24015,7 +24391,7 @@
       <c r="V934" s="1"/>
       <c r="W934" s="1"/>
     </row>
-    <row r="935" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="935" ht="12.75" customHeight="true">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -24040,7 +24416,7 @@
       <c r="V935" s="1"/>
       <c r="W935" s="1"/>
     </row>
-    <row r="936" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="936" ht="12.75" customHeight="true">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -24065,7 +24441,7 @@
       <c r="V936" s="1"/>
       <c r="W936" s="1"/>
     </row>
-    <row r="937" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="937" ht="12.75" customHeight="true">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -24090,7 +24466,7 @@
       <c r="V937" s="1"/>
       <c r="W937" s="1"/>
     </row>
-    <row r="938" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="938" ht="12.75" customHeight="true">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -24115,7 +24491,7 @@
       <c r="V938" s="1"/>
       <c r="W938" s="1"/>
     </row>
-    <row r="939" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="939" ht="12.75" customHeight="true">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -24140,7 +24516,7 @@
       <c r="V939" s="1"/>
       <c r="W939" s="1"/>
     </row>
-    <row r="940" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="940" ht="12.75" customHeight="true">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -24165,7 +24541,7 @@
       <c r="V940" s="1"/>
       <c r="W940" s="1"/>
     </row>
-    <row r="941" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="941" ht="12.75" customHeight="true">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -24190,7 +24566,7 @@
       <c r="V941" s="1"/>
       <c r="W941" s="1"/>
     </row>
-    <row r="942" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="942" ht="12.75" customHeight="true">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -24215,7 +24591,7 @@
       <c r="V942" s="1"/>
       <c r="W942" s="1"/>
     </row>
-    <row r="943" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="943" ht="12.75" customHeight="true">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -24240,7 +24616,7 @@
       <c r="V943" s="1"/>
       <c r="W943" s="1"/>
     </row>
-    <row r="944" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="944" ht="12.75" customHeight="true">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -24265,7 +24641,7 @@
       <c r="V944" s="1"/>
       <c r="W944" s="1"/>
     </row>
-    <row r="945" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="945" ht="12.75" customHeight="true">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -24290,7 +24666,7 @@
       <c r="V945" s="1"/>
       <c r="W945" s="1"/>
     </row>
-    <row r="946" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="946" ht="12.75" customHeight="true">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -24315,7 +24691,7 @@
       <c r="V946" s="1"/>
       <c r="W946" s="1"/>
     </row>
-    <row r="947" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="947" ht="12.75" customHeight="true">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -24340,7 +24716,7 @@
       <c r="V947" s="1"/>
       <c r="W947" s="1"/>
     </row>
-    <row r="948" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="948" ht="12.75" customHeight="true">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -24365,7 +24741,7 @@
       <c r="V948" s="1"/>
       <c r="W948" s="1"/>
     </row>
-    <row r="949" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="949" ht="12.75" customHeight="true">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -24390,7 +24766,7 @@
       <c r="V949" s="1"/>
       <c r="W949" s="1"/>
     </row>
-    <row r="950" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="950" ht="12.75" customHeight="true">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -24415,7 +24791,7 @@
       <c r="V950" s="1"/>
       <c r="W950" s="1"/>
     </row>
-    <row r="951" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="951" ht="12.75" customHeight="true">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -24440,7 +24816,7 @@
       <c r="V951" s="1"/>
       <c r="W951" s="1"/>
     </row>
-    <row r="952" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="952" ht="12.75" customHeight="true">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -24465,7 +24841,7 @@
       <c r="V952" s="1"/>
       <c r="W952" s="1"/>
     </row>
-    <row r="953" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="953" ht="12.75" customHeight="true">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -24490,7 +24866,7 @@
       <c r="V953" s="1"/>
       <c r="W953" s="1"/>
     </row>
-    <row r="954" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="954" ht="12.75" customHeight="true">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -24515,7 +24891,7 @@
       <c r="V954" s="1"/>
       <c r="W954" s="1"/>
     </row>
-    <row r="955" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="955" ht="12.75" customHeight="true">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -24540,7 +24916,7 @@
       <c r="V955" s="1"/>
       <c r="W955" s="1"/>
     </row>
-    <row r="956" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="956" ht="12.75" customHeight="true">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -24565,7 +24941,7 @@
       <c r="V956" s="1"/>
       <c r="W956" s="1"/>
     </row>
-    <row r="957" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="957" ht="12.75" customHeight="true">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -24590,7 +24966,7 @@
       <c r="V957" s="1"/>
       <c r="W957" s="1"/>
     </row>
-    <row r="958" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="958" ht="12.75" customHeight="true">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -24615,7 +24991,7 @@
       <c r="V958" s="1"/>
       <c r="W958" s="1"/>
     </row>
-    <row r="959" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="959" ht="12.75" customHeight="true">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -24640,7 +25016,7 @@
       <c r="V959" s="1"/>
       <c r="W959" s="1"/>
     </row>
-    <row r="960" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="960" ht="12.75" customHeight="true">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -24665,7 +25041,7 @@
       <c r="V960" s="1"/>
       <c r="W960" s="1"/>
     </row>
-    <row r="961" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="961" ht="12.75" customHeight="true">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -24690,7 +25066,7 @@
       <c r="V961" s="1"/>
       <c r="W961" s="1"/>
     </row>
-    <row r="962" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="962" ht="12.75" customHeight="true">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -24715,7 +25091,7 @@
       <c r="V962" s="1"/>
       <c r="W962" s="1"/>
     </row>
-    <row r="963" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="963" ht="12.75" customHeight="true">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -24740,7 +25116,7 @@
       <c r="V963" s="1"/>
       <c r="W963" s="1"/>
     </row>
-    <row r="964" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="964" ht="12.75" customHeight="true">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -24765,7 +25141,7 @@
       <c r="V964" s="1"/>
       <c r="W964" s="1"/>
     </row>
-    <row r="965" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="965" ht="12.75" customHeight="true">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -24790,7 +25166,7 @@
       <c r="V965" s="1"/>
       <c r="W965" s="1"/>
     </row>
-    <row r="966" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="966" ht="12.75" customHeight="true">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -24815,7 +25191,7 @@
       <c r="V966" s="1"/>
       <c r="W966" s="1"/>
     </row>
-    <row r="967" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="967" ht="12.75" customHeight="true">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -24840,7 +25216,7 @@
       <c r="V967" s="1"/>
       <c r="W967" s="1"/>
     </row>
-    <row r="968" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="968" ht="12.75" customHeight="true">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -24865,7 +25241,7 @@
       <c r="V968" s="1"/>
       <c r="W968" s="1"/>
     </row>
-    <row r="969" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="969" ht="12.75" customHeight="true">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -24890,7 +25266,7 @@
       <c r="V969" s="1"/>
       <c r="W969" s="1"/>
     </row>
-    <row r="970" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="970" ht="12.75" customHeight="true">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -24915,7 +25291,7 @@
       <c r="V970" s="1"/>
       <c r="W970" s="1"/>
     </row>
-    <row r="971" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="971" ht="12.75" customHeight="true">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -24940,7 +25316,7 @@
       <c r="V971" s="1"/>
       <c r="W971" s="1"/>
     </row>
-    <row r="972" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="972" ht="12.75" customHeight="true">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -24965,7 +25341,7 @@
       <c r="V972" s="1"/>
       <c r="W972" s="1"/>
     </row>
-    <row r="973" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="973" ht="12.75" customHeight="true">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -24990,7 +25366,7 @@
       <c r="V973" s="1"/>
       <c r="W973" s="1"/>
     </row>
-    <row r="974" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="974" ht="12.75" customHeight="true">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -25015,7 +25391,7 @@
       <c r="V974" s="1"/>
       <c r="W974" s="1"/>
     </row>
-    <row r="975" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="975" ht="12.75" customHeight="true">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -25040,7 +25416,7 @@
       <c r="V975" s="1"/>
       <c r="W975" s="1"/>
     </row>
-    <row r="976" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="976" ht="12.75" customHeight="true">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -25065,7 +25441,7 @@
       <c r="V976" s="1"/>
       <c r="W976" s="1"/>
     </row>
-    <row r="977" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="977" ht="12.75" customHeight="true">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -25090,7 +25466,7 @@
       <c r="V977" s="1"/>
       <c r="W977" s="1"/>
     </row>
-    <row r="978" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="978" ht="12.75" customHeight="true">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -25115,7 +25491,7 @@
       <c r="V978" s="1"/>
       <c r="W978" s="1"/>
     </row>
-    <row r="979" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="979" ht="12.75" customHeight="true">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -25140,7 +25516,7 @@
       <c r="V979" s="1"/>
       <c r="W979" s="1"/>
     </row>
-    <row r="980" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="980" ht="12.75" customHeight="true">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -25165,7 +25541,7 @@
       <c r="V980" s="1"/>
       <c r="W980" s="1"/>
     </row>
-    <row r="981" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="981" ht="12.75" customHeight="true">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -25190,7 +25566,7 @@
       <c r="V981" s="1"/>
       <c r="W981" s="1"/>
     </row>
-    <row r="982" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="982" ht="12.75" customHeight="true">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -25215,7 +25591,7 @@
       <c r="V982" s="1"/>
       <c r="W982" s="1"/>
     </row>
-    <row r="983" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="983" ht="12.75" customHeight="true">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -25240,7 +25616,7 @@
       <c r="V983" s="1"/>
       <c r="W983" s="1"/>
     </row>
-    <row r="984" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="984" ht="12.75" customHeight="true">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -25265,7 +25641,7 @@
       <c r="V984" s="1"/>
       <c r="W984" s="1"/>
     </row>
-    <row r="985" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="985" ht="12.75" customHeight="true">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -25290,7 +25666,7 @@
       <c r="V985" s="1"/>
       <c r="W985" s="1"/>
     </row>
-    <row r="986" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="986" ht="12.75" customHeight="true">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -25315,7 +25691,7 @@
       <c r="V986" s="1"/>
       <c r="W986" s="1"/>
     </row>
-    <row r="987" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="987" ht="12.75" customHeight="true">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -25340,7 +25716,7 @@
       <c r="V987" s="1"/>
       <c r="W987" s="1"/>
     </row>
-    <row r="988" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="988" ht="12.75" customHeight="true">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -25365,7 +25741,7 @@
       <c r="V988" s="1"/>
       <c r="W988" s="1"/>
     </row>
-    <row r="989" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="989" ht="12.75" customHeight="true">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -25390,7 +25766,7 @@
       <c r="V989" s="1"/>
       <c r="W989" s="1"/>
     </row>
-    <row r="990" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="990" ht="12.75" customHeight="true">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -25415,7 +25791,7 @@
       <c r="V990" s="1"/>
       <c r="W990" s="1"/>
     </row>
-    <row r="991" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="991" ht="12.75" customHeight="true">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -25440,7 +25816,7 @@
       <c r="V991" s="1"/>
       <c r="W991" s="1"/>
     </row>
-    <row r="992" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="992" ht="12.75" customHeight="true">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -25465,7 +25841,7 @@
       <c r="V992" s="1"/>
       <c r="W992" s="1"/>
     </row>
-    <row r="993" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="993" ht="12.75" customHeight="true">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -25490,7 +25866,7 @@
       <c r="V993" s="1"/>
       <c r="W993" s="1"/>
     </row>
-    <row r="994" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="994" ht="12.75" customHeight="true">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -25515,7 +25891,7 @@
       <c r="V994" s="1"/>
       <c r="W994" s="1"/>
     </row>
-    <row r="995" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="995" ht="12.75" customHeight="true">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -25540,7 +25916,7 @@
       <c r="V995" s="1"/>
       <c r="W995" s="1"/>
     </row>
-    <row r="996" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="996" ht="12.75" customHeight="true">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -25565,7 +25941,7 @@
       <c r="V996" s="1"/>
       <c r="W996" s="1"/>
     </row>
-    <row r="997" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="997" ht="12.75" customHeight="true">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -25590,7 +25966,7 @@
       <c r="V997" s="1"/>
       <c r="W997" s="1"/>
     </row>
-    <row r="998" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="998" ht="12.75" customHeight="true">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -25615,7 +25991,7 @@
       <c r="V998" s="1"/>
       <c r="W998" s="1"/>
     </row>
-    <row r="999" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="999" ht="12.75" customHeight="true">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -25640,7 +26016,7 @@
       <c r="V999" s="1"/>
       <c r="W999" s="1"/>
     </row>
-    <row r="1000" ht="12.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1000" ht="12.75" customHeight="true">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -25686,11 +26062,9 @@
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="A5:B5"/>
   </mergeCells>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;A</oddHeader>
-    <oddFooter>&amp;CPágina &amp;P</oddFooter>
-  </headerFooter>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <headerFooter alignWithMargins="1"/>
 </worksheet>
 </file>